--- a/restaurant_menus.xlsx
+++ b/restaurant_menus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ooredoomle-my.sharepoint.com/personal/ahmed_maail_ooredoo_mv/Documents/vishaal idea/ramadan menu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="11_F25DC773A252ABDACC1048D4395F6C085BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C62890B3-D242-4785-A771-2AF05D30AE9A}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_F25DC773A252ABDACC1048D4395F6C085BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{341788CB-D0EE-4A04-A7CE-14BE25915338}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="28">
   <si>
     <t>Day</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>monday</t>
+  </si>
+  <si>
+    <t>Price per Pax</t>
   </si>
 </sst>
 </file>
@@ -429,14 +432,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.42578125" customWidth="1"/>
     <col min="3" max="3" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -446,8 +449,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -457,8 +463,11 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -468,8 +477,11 @@
       <c r="C3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -479,8 +491,11 @@
       <c r="C4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -490,8 +505,11 @@
       <c r="C5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -501,8 +519,11 @@
       <c r="C6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -512,8 +533,11 @@
       <c r="C7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -523,8 +547,11 @@
       <c r="C8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -534,8 +561,11 @@
       <c r="C9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -545,8 +575,11 @@
       <c r="C10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -556,8 +589,11 @@
       <c r="C11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -567,8 +603,11 @@
       <c r="C12" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -578,8 +617,11 @@
       <c r="C13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -589,8 +631,11 @@
       <c r="C14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -600,8 +645,11 @@
       <c r="C15" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -611,8 +659,11 @@
       <c r="C16" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -622,8 +673,11 @@
       <c r="C17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -633,8 +687,11 @@
       <c r="C18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -644,8 +701,11 @@
       <c r="C21" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -655,8 +715,11 @@
       <c r="C22" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -666,8 +729,11 @@
       <c r="C23" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -677,8 +743,11 @@
       <c r="C24" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -688,8 +757,11 @@
       <c r="C25" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -699,8 +771,11 @@
       <c r="C26" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -710,8 +785,11 @@
       <c r="C27" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -721,8 +799,11 @@
       <c r="C28" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -732,8 +813,11 @@
       <c r="C29" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -743,8 +827,11 @@
       <c r="C30" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -754,8 +841,11 @@
       <c r="C31" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -765,8 +855,11 @@
       <c r="C32" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -776,8 +869,11 @@
       <c r="C33" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -787,8 +883,11 @@
       <c r="C34" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -798,8 +897,11 @@
       <c r="C35" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -809,8 +911,11 @@
       <c r="C36" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -819,6 +924,9 @@
       </c>
       <c r="C37" t="s">
         <v>19</v>
+      </c>
+      <c r="D37">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/restaurant_menus.xlsx
+++ b/restaurant_menus.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ooredoomle-my.sharepoint.com/personal/ahmed_maail_ooredoo_mv/Documents/vishaal idea/ramadan menu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="11_F25DC773A252ABDACC1048D4395F6C085BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{341788CB-D0EE-4A04-A7CE-14BE25915338}"/>
+  <xr:revisionPtr revIDLastSave="244" documentId="11_F25DC773A252ABDACC1048D4395F6C085BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C165C86B-95EB-4D07-A3D5-6E160A12EC94}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mamak" sheetId="1" r:id="rId1"/>
+    <sheet name="citron" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="124">
   <si>
     <t>Day</t>
   </si>
@@ -109,6 +110,294 @@
   </si>
   <si>
     <t>Price per Pax</t>
+  </si>
+  <si>
+    <t>Syrup Bandung</t>
+  </si>
+  <si>
+    <t>Chilli fries</t>
+  </si>
+  <si>
+    <t>Chicken Sliders</t>
+  </si>
+  <si>
+    <t>Rose pan</t>
+  </si>
+  <si>
+    <t>Butter Chicken Kottu</t>
+  </si>
+  <si>
+    <t>Peri Peri Chicken Rice</t>
+  </si>
+  <si>
+    <t>Chicken &amp; Potato Masala</t>
+  </si>
+  <si>
+    <t>Chilli Beef</t>
+  </si>
+  <si>
+    <t>Dhal curry</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Gulab Jamun</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>passion fruit juice</t>
+  </si>
+  <si>
+    <t>Kottu Kajaa</t>
+  </si>
+  <si>
+    <t>Chilli Kottu</t>
+  </si>
+  <si>
+    <t>Maqluba Rice</t>
+  </si>
+  <si>
+    <t>Stir Fry Veg</t>
+  </si>
+  <si>
+    <t>BBQ Chicken</t>
+  </si>
+  <si>
+    <t>Creamy Green Salad</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Karaa Fani</t>
+  </si>
+  <si>
+    <t>Fresh Fruit Juice</t>
+  </si>
+  <si>
+    <t>Mineral Water</t>
+  </si>
+  <si>
+    <t>Gulha</t>
+  </si>
+  <si>
+    <t>cutlets</t>
+  </si>
+  <si>
+    <t>pizza</t>
+  </si>
+  <si>
+    <t>Rice Porridge</t>
+  </si>
+  <si>
+    <t>Thai Omelette</t>
+  </si>
+  <si>
+    <t>Fen Folhi</t>
+  </si>
+  <si>
+    <t>Roshi</t>
+  </si>
+  <si>
+    <t>Farata</t>
+  </si>
+  <si>
+    <t>Cajun Chicken Fried Rice</t>
+  </si>
+  <si>
+    <t>Pasta with Napolitana Sauce</t>
+  </si>
+  <si>
+    <t>Thai Seafood Fried Noodles</t>
+  </si>
+  <si>
+    <t>Steamed Basmati Rice</t>
+  </si>
+  <si>
+    <t>Creamy Dijon Chicken</t>
+  </si>
+  <si>
+    <t>Kerala Style Beef Roast</t>
+  </si>
+  <si>
+    <t>Spicy Tawa Fish Fry</t>
+  </si>
+  <si>
+    <t>Brinjal Curry</t>
+  </si>
+  <si>
+    <t>Dhal fry</t>
+  </si>
+  <si>
+    <t>Kopeefathu Mas-Huni</t>
+  </si>
+  <si>
+    <t>Tuna Mas-Huni</t>
+  </si>
+  <si>
+    <t>Coleslaw Salad</t>
+  </si>
+  <si>
+    <t>Tossed Mixed Salad</t>
+  </si>
+  <si>
+    <t>Chocolate Biscuit Pudding</t>
+  </si>
+  <si>
+    <t>Red Velvet Cake</t>
+  </si>
+  <si>
+    <t>Strawberry Cheesecake</t>
+  </si>
+  <si>
+    <t>Fresh Fruit Salad</t>
+  </si>
+  <si>
+    <t>Betel Nuts</t>
+  </si>
+  <si>
+    <t>Chicken Biryani</t>
+  </si>
+  <si>
+    <t>Spaghetti with Afredo Sauce</t>
+  </si>
+  <si>
+    <t>Indonesian Bami Goreng</t>
+  </si>
+  <si>
+    <t>Beef Stroganoff</t>
+  </si>
+  <si>
+    <t>Fish Tikka Masala</t>
+  </si>
+  <si>
+    <t>Devilled Potatoes</t>
+  </si>
+  <si>
+    <t>Vegetable Curry</t>
+  </si>
+  <si>
+    <t>Kozhi Nirachathu</t>
+  </si>
+  <si>
+    <t>Green Papaga Salad</t>
+  </si>
+  <si>
+    <t>Chocolate Brownies</t>
+  </si>
+  <si>
+    <t>Vanilla Cheesecake</t>
+  </si>
+  <si>
+    <t>Crime Caramel</t>
+  </si>
+  <si>
+    <t>Mixed Meat Korean Rice</t>
+  </si>
+  <si>
+    <t>Cheesy Tuna Pasta Bake</t>
+  </si>
+  <si>
+    <t>Thai Egg Fried Noodles</t>
+  </si>
+  <si>
+    <t>Harissa Roasted Chicken</t>
+  </si>
+  <si>
+    <t>Pepper Beef Masala</t>
+  </si>
+  <si>
+    <t>Grilled Fish with Dill Cream Sauce</t>
+  </si>
+  <si>
+    <t>Tempered Dhal</t>
+  </si>
+  <si>
+    <t>Japanese Salad</t>
+  </si>
+  <si>
+    <t>Chocolate Chip Mousse</t>
+  </si>
+  <si>
+    <t>Lemon Mousse Cake</t>
+  </si>
+  <si>
+    <t>Pineapple Upside-Down Cake</t>
+  </si>
+  <si>
+    <t>Chicken Keema Rice</t>
+  </si>
+  <si>
+    <t>Beef lasagna</t>
+  </si>
+  <si>
+    <t>Chinese Mixed Fired Noodles</t>
+  </si>
+  <si>
+    <t>Chilli Chicken</t>
+  </si>
+  <si>
+    <t>Beef Rogan Josh</t>
+  </si>
+  <si>
+    <t>Fish Curry With Potatoes</t>
+  </si>
+  <si>
+    <t>Russian Salad</t>
+  </si>
+  <si>
+    <t>Tossed Green Salad</t>
+  </si>
+  <si>
+    <t>Moist Chocolate Cake</t>
+  </si>
+  <si>
+    <t>Coffee Creme Caramel</t>
+  </si>
+  <si>
+    <t>Chicken Kabsa</t>
+  </si>
+  <si>
+    <t>Penne Pasta with Marinara Sauce</t>
+  </si>
+  <si>
+    <t>Mongolian Chicken Noodles</t>
+  </si>
+  <si>
+    <t>Chicken Fricassee</t>
+  </si>
+  <si>
+    <t>Sri Lankan Beef Black Pepper Fry</t>
+  </si>
+  <si>
+    <t>Brinjal Moju</t>
+  </si>
+  <si>
+    <t>Dhal Fry</t>
+  </si>
+  <si>
+    <t>Chocolate Pudding</t>
+  </si>
+  <si>
+    <t>Creme Caramel</t>
+  </si>
+  <si>
+    <t>Oreo Cheesecake</t>
+  </si>
+  <si>
+    <t>260 per adult 150 per child</t>
   </si>
 </sst>
 </file>
@@ -432,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.42578125" customWidth="1"/>
@@ -464,7 +753,7 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>150</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -477,9 +766,6 @@
       <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D3">
-        <v>150</v>
-      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -491,9 +777,6 @@
       <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>150</v>
-      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -505,9 +788,6 @@
       <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="D5">
-        <v>150</v>
-      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -519,9 +799,6 @@
       <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D6">
-        <v>150</v>
-      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -533,9 +810,6 @@
       <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D7">
-        <v>150</v>
-      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -547,9 +821,6 @@
       <c r="C8" t="s">
         <v>9</v>
       </c>
-      <c r="D8">
-        <v>150</v>
-      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -561,9 +832,6 @@
       <c r="C9" t="s">
         <v>10</v>
       </c>
-      <c r="D9">
-        <v>150</v>
-      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -575,9 +843,6 @@
       <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="D10">
-        <v>150</v>
-      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -589,9 +854,6 @@
       <c r="C11" t="s">
         <v>12</v>
       </c>
-      <c r="D11">
-        <v>150</v>
-      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -603,9 +865,6 @@
       <c r="C12" t="s">
         <v>13</v>
       </c>
-      <c r="D12">
-        <v>150</v>
-      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -617,9 +876,6 @@
       <c r="C13" t="s">
         <v>14</v>
       </c>
-      <c r="D13">
-        <v>150</v>
-      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -631,9 +887,6 @@
       <c r="C14" t="s">
         <v>15</v>
       </c>
-      <c r="D14">
-        <v>150</v>
-      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -645,9 +898,6 @@
       <c r="C15" t="s">
         <v>16</v>
       </c>
-      <c r="D15">
-        <v>150</v>
-      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -659,9 +909,6 @@
       <c r="C16" t="s">
         <v>17</v>
       </c>
-      <c r="D16">
-        <v>150</v>
-      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -673,9 +920,6 @@
       <c r="C17" t="s">
         <v>18</v>
       </c>
-      <c r="D17">
-        <v>150</v>
-      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -687,8 +931,16 @@
       <c r="C18" t="s">
         <v>19</v>
       </c>
-      <c r="D18">
-        <v>150</v>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -702,7 +954,7 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -713,10 +965,7 @@
         <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22">
-        <v>200</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -727,10 +976,7 @@
         <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23">
-        <v>200</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -738,13 +984,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24">
-        <v>200</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -752,13 +995,10 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25">
-        <v>200</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -766,13 +1006,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26">
-        <v>200</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -780,13 +1017,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27">
-        <v>200</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -797,10 +1031,7 @@
         <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28">
-        <v>200</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -811,10 +1042,7 @@
         <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29">
-        <v>200</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -825,10 +1053,7 @@
         <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30">
-        <v>200</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -839,10 +1064,7 @@
         <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31">
-        <v>200</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -853,10 +1075,7 @@
         <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32">
-        <v>200</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -864,13 +1083,10 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33">
-        <v>200</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -878,13 +1094,10 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34">
-        <v>200</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -892,13 +1105,10 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35">
-        <v>200</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -906,13 +1116,10 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
-      </c>
-      <c r="D36">
-        <v>200</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -920,13 +1127,3387 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" t="s">
+        <v>23</v>
+      </c>
+      <c r="C55" t="s">
         <v>19</v>
       </c>
-      <c r="D37">
-        <v>200</v>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>40</v>
+      </c>
+      <c r="B59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>40</v>
+      </c>
+      <c r="B62" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>40</v>
+      </c>
+      <c r="B64" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>40</v>
+      </c>
+      <c r="B67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>40</v>
+      </c>
+      <c r="B69" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>40</v>
+      </c>
+      <c r="B70" t="s">
+        <v>22</v>
+      </c>
+      <c r="C70" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>40</v>
+      </c>
+      <c r="B71" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>40</v>
+      </c>
+      <c r="B72" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>40</v>
+      </c>
+      <c r="B73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C73" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>40</v>
+      </c>
+      <c r="B74" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>41</v>
+      </c>
+      <c r="B76" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>41</v>
+      </c>
+      <c r="B77" t="s">
+        <v>21</v>
+      </c>
+      <c r="C77" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>41</v>
+      </c>
+      <c r="B78" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>41</v>
+      </c>
+      <c r="B79" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>41</v>
+      </c>
+      <c r="B80" t="s">
+        <v>23</v>
+      </c>
+      <c r="C80" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>41</v>
+      </c>
+      <c r="B81" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>41</v>
+      </c>
+      <c r="B82" t="s">
+        <v>24</v>
+      </c>
+      <c r="C82" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>41</v>
+      </c>
+      <c r="B83" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>41</v>
+      </c>
+      <c r="B84" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>41</v>
+      </c>
+      <c r="B85" t="s">
+        <v>24</v>
+      </c>
+      <c r="C85" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>41</v>
+      </c>
+      <c r="B86" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>41</v>
+      </c>
+      <c r="B87" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>41</v>
+      </c>
+      <c r="B88" t="s">
+        <v>24</v>
+      </c>
+      <c r="C88" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>41</v>
+      </c>
+      <c r="B89" t="s">
+        <v>24</v>
+      </c>
+      <c r="C89" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>41</v>
+      </c>
+      <c r="B90" t="s">
+        <v>24</v>
+      </c>
+      <c r="C90" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>41</v>
+      </c>
+      <c r="B91" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>41</v>
+      </c>
+      <c r="B92" t="s">
+        <v>21</v>
+      </c>
+      <c r="C92" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>41</v>
+      </c>
+      <c r="B93" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>49</v>
+      </c>
+      <c r="B95" t="s">
+        <v>21</v>
+      </c>
+      <c r="C95" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>49</v>
+      </c>
+      <c r="B96" t="s">
+        <v>21</v>
+      </c>
+      <c r="C96" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>49</v>
+      </c>
+      <c r="B97" t="s">
+        <v>23</v>
+      </c>
+      <c r="C97" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>49</v>
+      </c>
+      <c r="B98" t="s">
+        <v>23</v>
+      </c>
+      <c r="C98" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>49</v>
+      </c>
+      <c r="B99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C99" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>49</v>
+      </c>
+      <c r="B100" t="s">
+        <v>24</v>
+      </c>
+      <c r="C100" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>49</v>
+      </c>
+      <c r="B101" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>49</v>
+      </c>
+      <c r="B102" t="s">
+        <v>24</v>
+      </c>
+      <c r="C102" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>49</v>
+      </c>
+      <c r="B103" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>49</v>
+      </c>
+      <c r="B104" t="s">
+        <v>24</v>
+      </c>
+      <c r="C104" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>49</v>
+      </c>
+      <c r="B105" t="s">
+        <v>24</v>
+      </c>
+      <c r="C105" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>49</v>
+      </c>
+      <c r="B106" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>49</v>
+      </c>
+      <c r="B107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C107" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>49</v>
+      </c>
+      <c r="B108" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>49</v>
+      </c>
+      <c r="B109" t="s">
+        <v>24</v>
+      </c>
+      <c r="C109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>49</v>
+      </c>
+      <c r="B110" t="s">
+        <v>23</v>
+      </c>
+      <c r="C110" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>49</v>
+      </c>
+      <c r="B111" t="s">
+        <v>21</v>
+      </c>
+      <c r="C111" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>49</v>
+      </c>
+      <c r="B112" t="s">
+        <v>22</v>
+      </c>
+      <c r="C112" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>50</v>
+      </c>
+      <c r="B114" t="s">
+        <v>21</v>
+      </c>
+      <c r="C114" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>50</v>
+      </c>
+      <c r="B115" t="s">
+        <v>21</v>
+      </c>
+      <c r="C115" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>50</v>
+      </c>
+      <c r="B116" t="s">
+        <v>23</v>
+      </c>
+      <c r="C116" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>50</v>
+      </c>
+      <c r="B117" t="s">
+        <v>23</v>
+      </c>
+      <c r="C117" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>50</v>
+      </c>
+      <c r="B118" t="s">
+        <v>23</v>
+      </c>
+      <c r="C118" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>50</v>
+      </c>
+      <c r="B119" t="s">
+        <v>24</v>
+      </c>
+      <c r="C119" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>50</v>
+      </c>
+      <c r="B120" t="s">
+        <v>24</v>
+      </c>
+      <c r="C120" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>50</v>
+      </c>
+      <c r="B121" t="s">
+        <v>24</v>
+      </c>
+      <c r="C121" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>50</v>
+      </c>
+      <c r="B122" t="s">
+        <v>24</v>
+      </c>
+      <c r="C122" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>50</v>
+      </c>
+      <c r="B123" t="s">
+        <v>24</v>
+      </c>
+      <c r="C123" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>50</v>
+      </c>
+      <c r="B124" t="s">
+        <v>24</v>
+      </c>
+      <c r="C124" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>50</v>
+      </c>
+      <c r="B125" t="s">
+        <v>24</v>
+      </c>
+      <c r="C125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>50</v>
+      </c>
+      <c r="B126" t="s">
+        <v>24</v>
+      </c>
+      <c r="C126" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>50</v>
+      </c>
+      <c r="B127" t="s">
+        <v>24</v>
+      </c>
+      <c r="C127" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>50</v>
+      </c>
+      <c r="B128" t="s">
+        <v>24</v>
+      </c>
+      <c r="C128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>50</v>
+      </c>
+      <c r="B129" t="s">
+        <v>23</v>
+      </c>
+      <c r="C129" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>50</v>
+      </c>
+      <c r="B130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C130" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>50</v>
+      </c>
+      <c r="B131" t="s">
+        <v>22</v>
+      </c>
+      <c r="C131" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958711E3-6C4F-4BD5-AB6C-48EB3BBDFE40}">
+  <dimension ref="A1:D220"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" t="s">
+        <v>51</v>
+      </c>
+      <c r="D64" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66" t="s">
+        <v>21</v>
+      </c>
+      <c r="C66" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>39</v>
+      </c>
+      <c r="B68" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>39</v>
+      </c>
+      <c r="B69" t="s">
+        <v>23</v>
+      </c>
+      <c r="C69" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>39</v>
+      </c>
+      <c r="B70" t="s">
+        <v>23</v>
+      </c>
+      <c r="C70" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>39</v>
+      </c>
+      <c r="B71" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>39</v>
+      </c>
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>39</v>
+      </c>
+      <c r="B73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>39</v>
+      </c>
+      <c r="B74" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>39</v>
+      </c>
+      <c r="B75" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>39</v>
+      </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>39</v>
+      </c>
+      <c r="B78" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>39</v>
+      </c>
+      <c r="B79" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>39</v>
+      </c>
+      <c r="B80" t="s">
+        <v>24</v>
+      </c>
+      <c r="C80" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>39</v>
+      </c>
+      <c r="B81" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>39</v>
+      </c>
+      <c r="B82" t="s">
+        <v>24</v>
+      </c>
+      <c r="C82" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>39</v>
+      </c>
+      <c r="B83" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>39</v>
+      </c>
+      <c r="B84" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>39</v>
+      </c>
+      <c r="B85" t="s">
+        <v>24</v>
+      </c>
+      <c r="C85" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>39</v>
+      </c>
+      <c r="B87" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>39</v>
+      </c>
+      <c r="B88" t="s">
+        <v>24</v>
+      </c>
+      <c r="C88" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89" t="s">
+        <v>22</v>
+      </c>
+      <c r="C89" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>39</v>
+      </c>
+      <c r="B90" t="s">
+        <v>22</v>
+      </c>
+      <c r="C90" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>39</v>
+      </c>
+      <c r="B91" t="s">
+        <v>22</v>
+      </c>
+      <c r="C91" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>39</v>
+      </c>
+      <c r="B92" t="s">
+        <v>22</v>
+      </c>
+      <c r="C92" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>39</v>
+      </c>
+      <c r="B93" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>40</v>
+      </c>
+      <c r="B95" t="s">
+        <v>21</v>
+      </c>
+      <c r="C95" t="s">
+        <v>51</v>
+      </c>
+      <c r="D95" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>40</v>
+      </c>
+      <c r="B96" t="s">
+        <v>21</v>
+      </c>
+      <c r="C96" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>40</v>
+      </c>
+      <c r="B97" t="s">
+        <v>21</v>
+      </c>
+      <c r="C97" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>40</v>
+      </c>
+      <c r="B98" t="s">
+        <v>23</v>
+      </c>
+      <c r="C98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>40</v>
+      </c>
+      <c r="B99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C99" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>40</v>
+      </c>
+      <c r="B100" t="s">
+        <v>23</v>
+      </c>
+      <c r="C100" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>40</v>
+      </c>
+      <c r="B101" t="s">
+        <v>23</v>
+      </c>
+      <c r="C101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>40</v>
+      </c>
+      <c r="B102" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>40</v>
+      </c>
+      <c r="B103" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>40</v>
+      </c>
+      <c r="B104" t="s">
+        <v>24</v>
+      </c>
+      <c r="C104" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>40</v>
+      </c>
+      <c r="B105" t="s">
+        <v>24</v>
+      </c>
+      <c r="C105" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>40</v>
+      </c>
+      <c r="B106" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>40</v>
+      </c>
+      <c r="B107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C107" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>40</v>
+      </c>
+      <c r="B108" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>40</v>
+      </c>
+      <c r="B109" t="s">
+        <v>24</v>
+      </c>
+      <c r="C109" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>40</v>
+      </c>
+      <c r="B110" t="s">
+        <v>24</v>
+      </c>
+      <c r="C110" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>40</v>
+      </c>
+      <c r="B111" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>40</v>
+      </c>
+      <c r="B112" t="s">
+        <v>24</v>
+      </c>
+      <c r="C112" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>40</v>
+      </c>
+      <c r="B113" t="s">
+        <v>24</v>
+      </c>
+      <c r="C113" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>40</v>
+      </c>
+      <c r="B114" t="s">
+        <v>24</v>
+      </c>
+      <c r="C114" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>40</v>
+      </c>
+      <c r="B115" t="s">
+        <v>24</v>
+      </c>
+      <c r="C115" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>40</v>
+      </c>
+      <c r="B116" t="s">
+        <v>24</v>
+      </c>
+      <c r="C116" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>40</v>
+      </c>
+      <c r="B117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>40</v>
+      </c>
+      <c r="B118" t="s">
+        <v>24</v>
+      </c>
+      <c r="C118" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>40</v>
+      </c>
+      <c r="B119" t="s">
+        <v>24</v>
+      </c>
+      <c r="C119" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>40</v>
+      </c>
+      <c r="B120" t="s">
+        <v>24</v>
+      </c>
+      <c r="C120" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>40</v>
+      </c>
+      <c r="B121" t="s">
+        <v>24</v>
+      </c>
+      <c r="C121" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>40</v>
+      </c>
+      <c r="B122" t="s">
+        <v>24</v>
+      </c>
+      <c r="C122" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>40</v>
+      </c>
+      <c r="B123" t="s">
+        <v>24</v>
+      </c>
+      <c r="C123" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>40</v>
+      </c>
+      <c r="B124" t="s">
+        <v>22</v>
+      </c>
+      <c r="C124" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>40</v>
+      </c>
+      <c r="B125" t="s">
+        <v>22</v>
+      </c>
+      <c r="C125" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>40</v>
+      </c>
+      <c r="B126" t="s">
+        <v>22</v>
+      </c>
+      <c r="C126" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>40</v>
+      </c>
+      <c r="B127" t="s">
+        <v>22</v>
+      </c>
+      <c r="C127" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>40</v>
+      </c>
+      <c r="B128" t="s">
+        <v>22</v>
+      </c>
+      <c r="C128" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>41</v>
+      </c>
+      <c r="B130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C130" t="s">
+        <v>51</v>
+      </c>
+      <c r="D130" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>41</v>
+      </c>
+      <c r="B131" t="s">
+        <v>21</v>
+      </c>
+      <c r="C131" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>41</v>
+      </c>
+      <c r="B132" t="s">
+        <v>21</v>
+      </c>
+      <c r="C132" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>41</v>
+      </c>
+      <c r="B133" t="s">
+        <v>23</v>
+      </c>
+      <c r="C133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>41</v>
+      </c>
+      <c r="B134" t="s">
+        <v>23</v>
+      </c>
+      <c r="C134" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>41</v>
+      </c>
+      <c r="B135" t="s">
+        <v>23</v>
+      </c>
+      <c r="C135" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>41</v>
+      </c>
+      <c r="B136" t="s">
+        <v>23</v>
+      </c>
+      <c r="C136" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>41</v>
+      </c>
+      <c r="B137" t="s">
+        <v>23</v>
+      </c>
+      <c r="C137" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>41</v>
+      </c>
+      <c r="B138" t="s">
+        <v>24</v>
+      </c>
+      <c r="C138" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>41</v>
+      </c>
+      <c r="B139" t="s">
+        <v>24</v>
+      </c>
+      <c r="C139" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>41</v>
+      </c>
+      <c r="B140" t="s">
+        <v>24</v>
+      </c>
+      <c r="C140" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>41</v>
+      </c>
+      <c r="B141" t="s">
+        <v>24</v>
+      </c>
+      <c r="C141" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>41</v>
+      </c>
+      <c r="B142" t="s">
+        <v>24</v>
+      </c>
+      <c r="C142" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>41</v>
+      </c>
+      <c r="B143" t="s">
+        <v>24</v>
+      </c>
+      <c r="C143" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>41</v>
+      </c>
+      <c r="B144" t="s">
+        <v>24</v>
+      </c>
+      <c r="C144" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>41</v>
+      </c>
+      <c r="B145" t="s">
+        <v>24</v>
+      </c>
+      <c r="C145" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>41</v>
+      </c>
+      <c r="B146" t="s">
+        <v>24</v>
+      </c>
+      <c r="C146" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>41</v>
+      </c>
+      <c r="B147" t="s">
+        <v>24</v>
+      </c>
+      <c r="C147" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>41</v>
+      </c>
+      <c r="B148" t="s">
+        <v>24</v>
+      </c>
+      <c r="C148" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>41</v>
+      </c>
+      <c r="B149" t="s">
+        <v>24</v>
+      </c>
+      <c r="C149" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>41</v>
+      </c>
+      <c r="B150" t="s">
+        <v>24</v>
+      </c>
+      <c r="C150" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>41</v>
+      </c>
+      <c r="B151" t="s">
+        <v>24</v>
+      </c>
+      <c r="C151" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>41</v>
+      </c>
+      <c r="B152" t="s">
+        <v>24</v>
+      </c>
+      <c r="C152" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>41</v>
+      </c>
+      <c r="B153" t="s">
+        <v>24</v>
+      </c>
+      <c r="C153" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>41</v>
+      </c>
+      <c r="B154" t="s">
+        <v>24</v>
+      </c>
+      <c r="C154" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>41</v>
+      </c>
+      <c r="B155" t="s">
+        <v>22</v>
+      </c>
+      <c r="C155" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>41</v>
+      </c>
+      <c r="B156" t="s">
+        <v>22</v>
+      </c>
+      <c r="C156" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>41</v>
+      </c>
+      <c r="B157" t="s">
+        <v>22</v>
+      </c>
+      <c r="C157" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>41</v>
+      </c>
+      <c r="B158" t="s">
+        <v>22</v>
+      </c>
+      <c r="C158" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>41</v>
+      </c>
+      <c r="B159" t="s">
+        <v>22</v>
+      </c>
+      <c r="C159" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>49</v>
+      </c>
+      <c r="B161" t="s">
+        <v>21</v>
+      </c>
+      <c r="C161" t="s">
+        <v>51</v>
+      </c>
+      <c r="D161" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>49</v>
+      </c>
+      <c r="B162" t="s">
+        <v>21</v>
+      </c>
+      <c r="C162" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>49</v>
+      </c>
+      <c r="B163" t="s">
+        <v>21</v>
+      </c>
+      <c r="C163" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>49</v>
+      </c>
+      <c r="B164" t="s">
+        <v>23</v>
+      </c>
+      <c r="C164" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>49</v>
+      </c>
+      <c r="B165" t="s">
+        <v>23</v>
+      </c>
+      <c r="C165" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>49</v>
+      </c>
+      <c r="B166" t="s">
+        <v>23</v>
+      </c>
+      <c r="C166" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>49</v>
+      </c>
+      <c r="B167" t="s">
+        <v>23</v>
+      </c>
+      <c r="C167" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>49</v>
+      </c>
+      <c r="B168" t="s">
+        <v>23</v>
+      </c>
+      <c r="C168" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>49</v>
+      </c>
+      <c r="B169" t="s">
+        <v>24</v>
+      </c>
+      <c r="C169" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>49</v>
+      </c>
+      <c r="B170" t="s">
+        <v>24</v>
+      </c>
+      <c r="C170" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>49</v>
+      </c>
+      <c r="B171" t="s">
+        <v>24</v>
+      </c>
+      <c r="C171" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>49</v>
+      </c>
+      <c r="B172" t="s">
+        <v>24</v>
+      </c>
+      <c r="C172" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>49</v>
+      </c>
+      <c r="B173" t="s">
+        <v>24</v>
+      </c>
+      <c r="C173" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>49</v>
+      </c>
+      <c r="B174" t="s">
+        <v>24</v>
+      </c>
+      <c r="C174" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>49</v>
+      </c>
+      <c r="B175" t="s">
+        <v>24</v>
+      </c>
+      <c r="C175" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>49</v>
+      </c>
+      <c r="B176" t="s">
+        <v>24</v>
+      </c>
+      <c r="C176" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>49</v>
+      </c>
+      <c r="B177" t="s">
+        <v>24</v>
+      </c>
+      <c r="C177" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>49</v>
+      </c>
+      <c r="B178" t="s">
+        <v>24</v>
+      </c>
+      <c r="C178" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>49</v>
+      </c>
+      <c r="B179" t="s">
+        <v>24</v>
+      </c>
+      <c r="C179" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>49</v>
+      </c>
+      <c r="B180" t="s">
+        <v>24</v>
+      </c>
+      <c r="C180" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>49</v>
+      </c>
+      <c r="B181" t="s">
+        <v>24</v>
+      </c>
+      <c r="C181" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>49</v>
+      </c>
+      <c r="B182" t="s">
+        <v>24</v>
+      </c>
+      <c r="C182" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>49</v>
+      </c>
+      <c r="B183" t="s">
+        <v>24</v>
+      </c>
+      <c r="C183" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>49</v>
+      </c>
+      <c r="B184" t="s">
+        <v>24</v>
+      </c>
+      <c r="C184" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>49</v>
+      </c>
+      <c r="B185" t="s">
+        <v>24</v>
+      </c>
+      <c r="C185" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>49</v>
+      </c>
+      <c r="B186" t="s">
+        <v>22</v>
+      </c>
+      <c r="C186" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>49</v>
+      </c>
+      <c r="B187" t="s">
+        <v>22</v>
+      </c>
+      <c r="C187" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>49</v>
+      </c>
+      <c r="B188" t="s">
+        <v>22</v>
+      </c>
+      <c r="C188" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>49</v>
+      </c>
+      <c r="B189" t="s">
+        <v>22</v>
+      </c>
+      <c r="C189" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>50</v>
+      </c>
+      <c r="B191" t="s">
+        <v>21</v>
+      </c>
+      <c r="C191" t="s">
+        <v>51</v>
+      </c>
+      <c r="D191" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>50</v>
+      </c>
+      <c r="B192" t="s">
+        <v>21</v>
+      </c>
+      <c r="C192" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>50</v>
+      </c>
+      <c r="B193" t="s">
+        <v>21</v>
+      </c>
+      <c r="C193" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>50</v>
+      </c>
+      <c r="B194" t="s">
+        <v>23</v>
+      </c>
+      <c r="C194" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>50</v>
+      </c>
+      <c r="B195" t="s">
+        <v>23</v>
+      </c>
+      <c r="C195" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>50</v>
+      </c>
+      <c r="B196" t="s">
+        <v>23</v>
+      </c>
+      <c r="C196" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>50</v>
+      </c>
+      <c r="B197" t="s">
+        <v>23</v>
+      </c>
+      <c r="C197" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>50</v>
+      </c>
+      <c r="B198" t="s">
+        <v>23</v>
+      </c>
+      <c r="C198" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>50</v>
+      </c>
+      <c r="B199" t="s">
+        <v>24</v>
+      </c>
+      <c r="C199" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>50</v>
+      </c>
+      <c r="B200" t="s">
+        <v>24</v>
+      </c>
+      <c r="C200" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>50</v>
+      </c>
+      <c r="B201" t="s">
+        <v>24</v>
+      </c>
+      <c r="C201" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>50</v>
+      </c>
+      <c r="B202" t="s">
+        <v>24</v>
+      </c>
+      <c r="C202" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>50</v>
+      </c>
+      <c r="B203" t="s">
+        <v>24</v>
+      </c>
+      <c r="C203" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>50</v>
+      </c>
+      <c r="B204" t="s">
+        <v>24</v>
+      </c>
+      <c r="C204" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>50</v>
+      </c>
+      <c r="B205" t="s">
+        <v>24</v>
+      </c>
+      <c r="C205" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>50</v>
+      </c>
+      <c r="B206" t="s">
+        <v>24</v>
+      </c>
+      <c r="C206" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>50</v>
+      </c>
+      <c r="B207" t="s">
+        <v>24</v>
+      </c>
+      <c r="C207" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>50</v>
+      </c>
+      <c r="B208" t="s">
+        <v>24</v>
+      </c>
+      <c r="C208" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>50</v>
+      </c>
+      <c r="B209" t="s">
+        <v>24</v>
+      </c>
+      <c r="C209" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>50</v>
+      </c>
+      <c r="B210" t="s">
+        <v>24</v>
+      </c>
+      <c r="C210" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>50</v>
+      </c>
+      <c r="B211" t="s">
+        <v>24</v>
+      </c>
+      <c r="C211" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>50</v>
+      </c>
+      <c r="B212" t="s">
+        <v>24</v>
+      </c>
+      <c r="C212" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>50</v>
+      </c>
+      <c r="B213" t="s">
+        <v>24</v>
+      </c>
+      <c r="C213" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>50</v>
+      </c>
+      <c r="B214" t="s">
+        <v>24</v>
+      </c>
+      <c r="C214" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>50</v>
+      </c>
+      <c r="B215" t="s">
+        <v>24</v>
+      </c>
+      <c r="C215" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>50</v>
+      </c>
+      <c r="B216" t="s">
+        <v>22</v>
+      </c>
+      <c r="C216" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>50</v>
+      </c>
+      <c r="B217" t="s">
+        <v>22</v>
+      </c>
+      <c r="C217" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>50</v>
+      </c>
+      <c r="B218" t="s">
+        <v>22</v>
+      </c>
+      <c r="C218" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>50</v>
+      </c>
+      <c r="B219" t="s">
+        <v>22</v>
+      </c>
+      <c r="C219" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>50</v>
+      </c>
+      <c r="B220" t="s">
+        <v>22</v>
+      </c>
+      <c r="C220" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/restaurant_menus.xlsx
+++ b/restaurant_menus.xlsx
@@ -8,25 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ooredoomle-my.sharepoint.com/personal/ahmed_maail_ooredoo_mv/Documents/vishaal idea/ramadan menu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="244" documentId="11_F25DC773A252ABDACC1048D4395F6C085BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C165C86B-95EB-4D07-A3D5-6E160A12EC94}"/>
+  <xr:revisionPtr revIDLastSave="257" documentId="11_F25DC773A252ABDACC1048D4395F6C085BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D047379-E370-4655-A106-07AAC918A408}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mamak" sheetId="1" r:id="rId1"/>
     <sheet name="citron" sheetId="2" r:id="rId2"/>
+    <sheet name="pomelo" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="124">
   <si>
     <t>Day</t>
   </si>
@@ -37,15 +49,30 @@
     <t>Food Item</t>
   </si>
   <si>
+    <t>Price per Pax</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>drinks</t>
+  </si>
+  <si>
     <t>Watermelon Juice</t>
   </si>
   <si>
     <t>Pineapple Juice</t>
   </si>
   <si>
+    <t>Starters</t>
+  </si>
+  <si>
     <t>Club Sandwich</t>
   </si>
   <si>
+    <t>Desserts</t>
+  </si>
+  <si>
     <t>Nuts / Water</t>
   </si>
   <si>
@@ -58,6 +85,9 @@
     <t>Fresh Fruits</t>
   </si>
   <si>
+    <t>Main Dishes</t>
+  </si>
+  <si>
     <t>Mahalabia</t>
   </si>
   <si>
@@ -88,19 +118,7 @@
     <t>Mini Burgers</t>
   </si>
   <si>
-    <t>Sunday</t>
-  </si>
-  <si>
-    <t>drinks</t>
-  </si>
-  <si>
-    <t>Desserts</t>
-  </si>
-  <si>
-    <t>Starters</t>
-  </si>
-  <si>
-    <t>Main Dishes</t>
+    <t>Syrup Bandung</t>
   </si>
   <si>
     <t>Monday</t>
@@ -109,12 +127,6 @@
     <t>monday</t>
   </si>
   <si>
-    <t>Price per Pax</t>
-  </si>
-  <si>
-    <t>Syrup Bandung</t>
-  </si>
-  <si>
     <t>Chilli fries</t>
   </si>
   <si>
@@ -184,6 +196,9 @@
     <t>Karaa Fani</t>
   </si>
   <si>
+    <t>260 per adult 150 per child</t>
+  </si>
+  <si>
     <t>Fresh Fruit Juice</t>
   </si>
   <si>
@@ -277,6 +292,9 @@
     <t>Indonesian Bami Goreng</t>
   </si>
   <si>
+    <t>Kozhi Nirachathu</t>
+  </si>
+  <si>
     <t>Beef Stroganoff</t>
   </si>
   <si>
@@ -289,9 +307,6 @@
     <t>Vegetable Curry</t>
   </si>
   <si>
-    <t>Kozhi Nirachathu</t>
-  </si>
-  <si>
     <t>Green Papaga Salad</t>
   </si>
   <si>
@@ -395,9 +410,6 @@
   </si>
   <si>
     <t>Oreo Cheesecake</t>
-  </si>
-  <si>
-    <t>260 per adult 150 per child</t>
   </si>
 </sst>
 </file>
@@ -739,18 +751,18 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>195</v>
@@ -758,200 +770,200 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
         <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>195</v>
@@ -959,21 +971,21 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
         <v>26</v>
-      </c>
-      <c r="B22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
@@ -981,10 +993,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
         <v>30</v>
@@ -992,10 +1004,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
         <v>31</v>
@@ -1003,10 +1015,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C26" t="s">
         <v>32</v>
@@ -1014,10 +1026,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C27" t="s">
         <v>33</v>
@@ -1025,10 +1037,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
         <v>34</v>
@@ -1036,10 +1048,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
         <v>35</v>
@@ -1047,10 +1059,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C30" t="s">
         <v>36</v>
@@ -1058,10 +1070,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
         <v>37</v>
@@ -1069,21 +1081,21 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C33" t="s">
         <v>38</v>
@@ -1091,46 +1103,46 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1138,10 +1150,10 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D39">
         <v>195</v>
@@ -1152,10 +1164,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1163,10 +1175,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1174,10 +1186,10 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1185,10 +1197,10 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1196,10 +1208,10 @@
         <v>39</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1207,10 +1219,10 @@
         <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1218,10 +1230,10 @@
         <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1229,10 +1241,10 @@
         <v>39</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1240,10 +1252,10 @@
         <v>39</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1251,10 +1263,10 @@
         <v>39</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1262,10 +1274,10 @@
         <v>39</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1273,10 +1285,10 @@
         <v>39</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1284,10 +1296,10 @@
         <v>39</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1295,10 +1307,10 @@
         <v>39</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C53" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1306,10 +1318,10 @@
         <v>39</v>
       </c>
       <c r="B54" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C54" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1317,10 +1329,10 @@
         <v>39</v>
       </c>
       <c r="B55" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1328,10 +1340,10 @@
         <v>39</v>
       </c>
       <c r="B56" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -1339,10 +1351,10 @@
         <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D58">
         <v>195</v>
@@ -1353,10 +1365,10 @@
         <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C59" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1364,7 +1376,7 @@
         <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C60" t="s">
         <v>29</v>
@@ -1375,7 +1387,7 @@
         <v>40</v>
       </c>
       <c r="B61" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C61" t="s">
         <v>30</v>
@@ -1386,7 +1398,7 @@
         <v>40</v>
       </c>
       <c r="B62" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C62" t="s">
         <v>31</v>
@@ -1397,7 +1409,7 @@
         <v>40</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -1408,7 +1420,7 @@
         <v>40</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C64" t="s">
         <v>33</v>
@@ -1419,7 +1431,7 @@
         <v>40</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C65" t="s">
         <v>34</v>
@@ -1430,7 +1442,7 @@
         <v>40</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C66" t="s">
         <v>35</v>
@@ -1441,7 +1453,7 @@
         <v>40</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C67" t="s">
         <v>36</v>
@@ -1452,7 +1464,7 @@
         <v>40</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C68" t="s">
         <v>37</v>
@@ -1463,10 +1475,10 @@
         <v>40</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C69" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -1474,7 +1486,7 @@
         <v>40</v>
       </c>
       <c r="B70" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C70" t="s">
         <v>38</v>
@@ -1485,10 +1497,10 @@
         <v>40</v>
       </c>
       <c r="B71" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -1496,10 +1508,10 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -1507,10 +1519,10 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C73" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -1518,10 +1530,10 @@
         <v>40</v>
       </c>
       <c r="B74" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -1529,10 +1541,10 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C76" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D76">
         <v>210</v>
@@ -1543,7 +1555,7 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C77" t="s">
         <v>42</v>
@@ -1554,7 +1566,7 @@
         <v>41</v>
       </c>
       <c r="B78" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C78" t="s">
         <v>43</v>
@@ -1565,7 +1577,7 @@
         <v>41</v>
       </c>
       <c r="B79" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C79" t="s">
         <v>30</v>
@@ -1576,10 +1588,10 @@
         <v>41</v>
       </c>
       <c r="B80" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1587,7 +1599,7 @@
         <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C81" t="s">
         <v>44</v>
@@ -1598,10 +1610,10 @@
         <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C82" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -1609,7 +1621,7 @@
         <v>41</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C83" t="s">
         <v>45</v>
@@ -1620,7 +1632,7 @@
         <v>41</v>
       </c>
       <c r="B84" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C84" t="s">
         <v>46</v>
@@ -1631,7 +1643,7 @@
         <v>41</v>
       </c>
       <c r="B85" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C85" t="s">
         <v>47</v>
@@ -1642,10 +1654,10 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C86" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -1653,10 +1665,10 @@
         <v>41</v>
       </c>
       <c r="B87" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C87" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -1664,7 +1676,7 @@
         <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C88" t="s">
         <v>48</v>
@@ -1675,10 +1687,10 @@
         <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C89" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -1686,10 +1698,10 @@
         <v>41</v>
       </c>
       <c r="B90" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C90" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -1697,10 +1709,10 @@
         <v>41</v>
       </c>
       <c r="B91" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -1708,10 +1720,10 @@
         <v>41</v>
       </c>
       <c r="B92" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C92" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -1719,10 +1731,10 @@
         <v>41</v>
       </c>
       <c r="B93" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -1730,10 +1742,10 @@
         <v>49</v>
       </c>
       <c r="B95" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C95" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D95">
         <v>210</v>
@@ -1744,7 +1756,7 @@
         <v>49</v>
       </c>
       <c r="B96" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C96" t="s">
         <v>42</v>
@@ -1755,7 +1767,7 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C97" t="s">
         <v>43</v>
@@ -1766,7 +1778,7 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C98" t="s">
         <v>30</v>
@@ -1777,10 +1789,10 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -1788,7 +1800,7 @@
         <v>49</v>
       </c>
       <c r="B100" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C100" t="s">
         <v>44</v>
@@ -1799,10 +1811,10 @@
         <v>49</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C101" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -1810,7 +1822,7 @@
         <v>49</v>
       </c>
       <c r="B102" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C102" t="s">
         <v>45</v>
@@ -1821,7 +1833,7 @@
         <v>49</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C103" t="s">
         <v>46</v>
@@ -1832,7 +1844,7 @@
         <v>49</v>
       </c>
       <c r="B104" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C104" t="s">
         <v>47</v>
@@ -1843,10 +1855,10 @@
         <v>49</v>
       </c>
       <c r="B105" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C105" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -1854,10 +1866,10 @@
         <v>49</v>
       </c>
       <c r="B106" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C106" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -1865,7 +1877,7 @@
         <v>49</v>
       </c>
       <c r="B107" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C107" t="s">
         <v>48</v>
@@ -1876,10 +1888,10 @@
         <v>49</v>
       </c>
       <c r="B108" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C108" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -1887,10 +1899,10 @@
         <v>49</v>
       </c>
       <c r="B109" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C109" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -1898,10 +1910,10 @@
         <v>49</v>
       </c>
       <c r="B110" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C110" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -1909,10 +1921,10 @@
         <v>49</v>
       </c>
       <c r="B111" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C111" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -1920,10 +1932,10 @@
         <v>49</v>
       </c>
       <c r="B112" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C112" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -1931,10 +1943,10 @@
         <v>50</v>
       </c>
       <c r="B114" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C114" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D114">
         <v>210</v>
@@ -1945,7 +1957,7 @@
         <v>50</v>
       </c>
       <c r="B115" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C115" t="s">
         <v>42</v>
@@ -1956,7 +1968,7 @@
         <v>50</v>
       </c>
       <c r="B116" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C116" t="s">
         <v>43</v>
@@ -1967,7 +1979,7 @@
         <v>50</v>
       </c>
       <c r="B117" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C117" t="s">
         <v>30</v>
@@ -1978,10 +1990,10 @@
         <v>50</v>
       </c>
       <c r="B118" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -1989,7 +2001,7 @@
         <v>50</v>
       </c>
       <c r="B119" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C119" t="s">
         <v>44</v>
@@ -2000,10 +2012,10 @@
         <v>50</v>
       </c>
       <c r="B120" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C120" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -2011,7 +2023,7 @@
         <v>50</v>
       </c>
       <c r="B121" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C121" t="s">
         <v>45</v>
@@ -2022,7 +2034,7 @@
         <v>50</v>
       </c>
       <c r="B122" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C122" t="s">
         <v>46</v>
@@ -2033,7 +2045,7 @@
         <v>50</v>
       </c>
       <c r="B123" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C123" t="s">
         <v>47</v>
@@ -2044,10 +2056,10 @@
         <v>50</v>
       </c>
       <c r="B124" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C124" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -2055,10 +2067,10 @@
         <v>50</v>
       </c>
       <c r="B125" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C125" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -2066,7 +2078,7 @@
         <v>50</v>
       </c>
       <c r="B126" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C126" t="s">
         <v>48</v>
@@ -2077,10 +2089,10 @@
         <v>50</v>
       </c>
       <c r="B127" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C127" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -2088,10 +2100,10 @@
         <v>50</v>
       </c>
       <c r="B128" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C128" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -2099,10 +2111,10 @@
         <v>50</v>
       </c>
       <c r="B129" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -2110,10 +2122,10 @@
         <v>50</v>
       </c>
       <c r="B130" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C130" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -2121,10 +2133,10 @@
         <v>50</v>
       </c>
       <c r="B131" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C131" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2154,662 +2166,662 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C34" t="s">
         <v>51</v>
       </c>
       <c r="D34" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C53" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C54" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C57" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C58" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C59" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B60" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -2817,13 +2829,13 @@
         <v>39</v>
       </c>
       <c r="B64" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C64" t="s">
         <v>51</v>
       </c>
       <c r="D64" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2831,10 +2843,10 @@
         <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2842,10 +2854,10 @@
         <v>39</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2853,10 +2865,10 @@
         <v>39</v>
       </c>
       <c r="B67" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -2864,10 +2876,10 @@
         <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -2875,10 +2887,10 @@
         <v>39</v>
       </c>
       <c r="B69" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -2886,10 +2898,10 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -2897,10 +2909,10 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -2908,10 +2920,10 @@
         <v>39</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C72" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -2919,10 +2931,10 @@
         <v>39</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C73" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -2930,10 +2942,10 @@
         <v>39</v>
       </c>
       <c r="B74" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C74" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -2941,10 +2953,10 @@
         <v>39</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C75" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -2952,10 +2964,10 @@
         <v>39</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -2963,10 +2975,10 @@
         <v>39</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C77" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -2974,10 +2986,10 @@
         <v>39</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C78" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -2985,10 +2997,10 @@
         <v>39</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C79" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -2996,10 +3008,10 @@
         <v>39</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C80" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -3007,10 +3019,10 @@
         <v>39</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -3018,10 +3030,10 @@
         <v>39</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C82" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -3029,10 +3041,10 @@
         <v>39</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C83" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -3040,10 +3052,10 @@
         <v>39</v>
       </c>
       <c r="B84" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C84" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -3051,10 +3063,10 @@
         <v>39</v>
       </c>
       <c r="B85" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -3062,10 +3074,10 @@
         <v>39</v>
       </c>
       <c r="B86" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C86" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -3073,10 +3085,10 @@
         <v>39</v>
       </c>
       <c r="B87" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C87" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -3084,10 +3096,10 @@
         <v>39</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C88" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -3095,10 +3107,10 @@
         <v>39</v>
       </c>
       <c r="B89" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -3106,10 +3118,10 @@
         <v>39</v>
       </c>
       <c r="B90" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C90" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -3117,10 +3129,10 @@
         <v>39</v>
       </c>
       <c r="B91" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -3128,10 +3140,10 @@
         <v>39</v>
       </c>
       <c r="B92" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -3139,10 +3151,10 @@
         <v>39</v>
       </c>
       <c r="B93" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -3150,13 +3162,13 @@
         <v>40</v>
       </c>
       <c r="B95" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C95" t="s">
         <v>51</v>
       </c>
       <c r="D95" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -3164,10 +3176,10 @@
         <v>40</v>
       </c>
       <c r="B96" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C96" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3175,10 +3187,10 @@
         <v>40</v>
       </c>
       <c r="B97" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3186,10 +3198,10 @@
         <v>40</v>
       </c>
       <c r="B98" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3197,10 +3209,10 @@
         <v>40</v>
       </c>
       <c r="B99" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3208,10 +3220,10 @@
         <v>40</v>
       </c>
       <c r="B100" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3219,10 +3231,10 @@
         <v>40</v>
       </c>
       <c r="B101" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3230,10 +3242,10 @@
         <v>40</v>
       </c>
       <c r="B102" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C102" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3241,10 +3253,10 @@
         <v>40</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C103" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3252,10 +3264,10 @@
         <v>40</v>
       </c>
       <c r="B104" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C104" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3263,10 +3275,10 @@
         <v>40</v>
       </c>
       <c r="B105" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C105" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3274,10 +3286,10 @@
         <v>40</v>
       </c>
       <c r="B106" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C106" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3285,10 +3297,10 @@
         <v>40</v>
       </c>
       <c r="B107" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C107" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3296,10 +3308,10 @@
         <v>40</v>
       </c>
       <c r="B108" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C108" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3307,10 +3319,10 @@
         <v>40</v>
       </c>
       <c r="B109" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C109" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3318,10 +3330,10 @@
         <v>40</v>
       </c>
       <c r="B110" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C110" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3329,10 +3341,10 @@
         <v>40</v>
       </c>
       <c r="B111" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C111" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3340,10 +3352,10 @@
         <v>40</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C112" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3351,10 +3363,10 @@
         <v>40</v>
       </c>
       <c r="B113" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C113" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3362,10 +3374,10 @@
         <v>40</v>
       </c>
       <c r="B114" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C114" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3373,10 +3385,10 @@
         <v>40</v>
       </c>
       <c r="B115" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C115" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3384,10 +3396,10 @@
         <v>40</v>
       </c>
       <c r="B116" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C116" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3395,10 +3407,10 @@
         <v>40</v>
       </c>
       <c r="B117" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C117" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3406,10 +3418,10 @@
         <v>40</v>
       </c>
       <c r="B118" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C118" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3417,10 +3429,10 @@
         <v>40</v>
       </c>
       <c r="B119" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C119" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3428,10 +3440,10 @@
         <v>40</v>
       </c>
       <c r="B120" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C120" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3439,10 +3451,10 @@
         <v>40</v>
       </c>
       <c r="B121" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C121" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3450,10 +3462,10 @@
         <v>40</v>
       </c>
       <c r="B122" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C122" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3461,10 +3473,10 @@
         <v>40</v>
       </c>
       <c r="B123" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C123" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3472,10 +3484,10 @@
         <v>40</v>
       </c>
       <c r="B124" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C124" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3483,10 +3495,10 @@
         <v>40</v>
       </c>
       <c r="B125" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C125" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3494,10 +3506,10 @@
         <v>40</v>
       </c>
       <c r="B126" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C126" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3505,10 +3517,10 @@
         <v>40</v>
       </c>
       <c r="B127" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C127" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3516,10 +3528,10 @@
         <v>40</v>
       </c>
       <c r="B128" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C128" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -3527,13 +3539,13 @@
         <v>41</v>
       </c>
       <c r="B130" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C130" t="s">
         <v>51</v>
       </c>
       <c r="D130" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
@@ -3541,10 +3553,10 @@
         <v>41</v>
       </c>
       <c r="B131" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C131" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
@@ -3552,10 +3564,10 @@
         <v>41</v>
       </c>
       <c r="B132" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C132" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
@@ -3563,10 +3575,10 @@
         <v>41</v>
       </c>
       <c r="B133" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C133" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
@@ -3574,10 +3586,10 @@
         <v>41</v>
       </c>
       <c r="B134" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C134" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -3585,10 +3597,10 @@
         <v>41</v>
       </c>
       <c r="B135" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C135" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -3596,10 +3608,10 @@
         <v>41</v>
       </c>
       <c r="B136" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C136" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -3607,10 +3619,10 @@
         <v>41</v>
       </c>
       <c r="B137" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C137" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
@@ -3618,10 +3630,10 @@
         <v>41</v>
       </c>
       <c r="B138" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C138" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -3629,10 +3641,10 @@
         <v>41</v>
       </c>
       <c r="B139" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
@@ -3640,10 +3652,10 @@
         <v>41</v>
       </c>
       <c r="B140" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C140" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
@@ -3651,10 +3663,10 @@
         <v>41</v>
       </c>
       <c r="B141" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C141" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -3662,10 +3674,10 @@
         <v>41</v>
       </c>
       <c r="B142" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C142" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -3673,10 +3685,10 @@
         <v>41</v>
       </c>
       <c r="B143" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C143" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -3684,10 +3696,10 @@
         <v>41</v>
       </c>
       <c r="B144" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C144" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3695,10 +3707,10 @@
         <v>41</v>
       </c>
       <c r="B145" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C145" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3706,10 +3718,10 @@
         <v>41</v>
       </c>
       <c r="B146" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C146" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3717,10 +3729,10 @@
         <v>41</v>
       </c>
       <c r="B147" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C147" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3728,10 +3740,10 @@
         <v>41</v>
       </c>
       <c r="B148" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C148" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3739,10 +3751,10 @@
         <v>41</v>
       </c>
       <c r="B149" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C149" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3750,10 +3762,10 @@
         <v>41</v>
       </c>
       <c r="B150" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C150" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3761,10 +3773,10 @@
         <v>41</v>
       </c>
       <c r="B151" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C151" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3772,10 +3784,10 @@
         <v>41</v>
       </c>
       <c r="B152" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C152" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3783,10 +3795,10 @@
         <v>41</v>
       </c>
       <c r="B153" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C153" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3794,10 +3806,10 @@
         <v>41</v>
       </c>
       <c r="B154" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C154" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3805,10 +3817,10 @@
         <v>41</v>
       </c>
       <c r="B155" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C155" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3816,10 +3828,10 @@
         <v>41</v>
       </c>
       <c r="B156" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C156" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3827,10 +3839,10 @@
         <v>41</v>
       </c>
       <c r="B157" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C157" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3838,10 +3850,10 @@
         <v>41</v>
       </c>
       <c r="B158" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C158" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3849,10 +3861,10 @@
         <v>41</v>
       </c>
       <c r="B159" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C159" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -3860,13 +3872,13 @@
         <v>49</v>
       </c>
       <c r="B161" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C161" t="s">
         <v>51</v>
       </c>
       <c r="D161" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
@@ -3874,10 +3886,10 @@
         <v>49</v>
       </c>
       <c r="B162" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C162" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -3885,10 +3897,10 @@
         <v>49</v>
       </c>
       <c r="B163" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C163" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
@@ -3896,10 +3908,10 @@
         <v>49</v>
       </c>
       <c r="B164" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
@@ -3907,10 +3919,10 @@
         <v>49</v>
       </c>
       <c r="B165" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -3918,10 +3930,10 @@
         <v>49</v>
       </c>
       <c r="B166" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
@@ -3929,10 +3941,10 @@
         <v>49</v>
       </c>
       <c r="B167" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
@@ -3940,10 +3952,10 @@
         <v>49</v>
       </c>
       <c r="B168" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
@@ -3951,10 +3963,10 @@
         <v>49</v>
       </c>
       <c r="B169" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C169" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
@@ -3962,10 +3974,10 @@
         <v>49</v>
       </c>
       <c r="B170" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C170" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
@@ -3973,10 +3985,10 @@
         <v>49</v>
       </c>
       <c r="B171" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C171" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
@@ -3984,10 +3996,10 @@
         <v>49</v>
       </c>
       <c r="B172" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C172" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
@@ -3995,10 +4007,10 @@
         <v>49</v>
       </c>
       <c r="B173" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C173" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
@@ -4006,10 +4018,10 @@
         <v>49</v>
       </c>
       <c r="B174" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C174" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
@@ -4017,10 +4029,10 @@
         <v>49</v>
       </c>
       <c r="B175" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C175" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
@@ -4028,10 +4040,10 @@
         <v>49</v>
       </c>
       <c r="B176" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C176" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
@@ -4039,10 +4051,10 @@
         <v>49</v>
       </c>
       <c r="B177" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C177" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -4050,10 +4062,10 @@
         <v>49</v>
       </c>
       <c r="B178" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C178" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
@@ -4061,10 +4073,10 @@
         <v>49</v>
       </c>
       <c r="B179" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C179" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
@@ -4072,10 +4084,10 @@
         <v>49</v>
       </c>
       <c r="B180" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C180" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
@@ -4083,10 +4095,10 @@
         <v>49</v>
       </c>
       <c r="B181" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C181" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
@@ -4094,10 +4106,10 @@
         <v>49</v>
       </c>
       <c r="B182" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C182" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
@@ -4105,10 +4117,10 @@
         <v>49</v>
       </c>
       <c r="B183" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C183" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
@@ -4116,10 +4128,10 @@
         <v>49</v>
       </c>
       <c r="B184" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C184" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
@@ -4127,10 +4139,10 @@
         <v>49</v>
       </c>
       <c r="B185" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C185" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
@@ -4138,10 +4150,10 @@
         <v>49</v>
       </c>
       <c r="B186" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C186" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
@@ -4149,10 +4161,10 @@
         <v>49</v>
       </c>
       <c r="B187" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C187" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
@@ -4160,10 +4172,10 @@
         <v>49</v>
       </c>
       <c r="B188" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C188" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
@@ -4171,10 +4183,10 @@
         <v>49</v>
       </c>
       <c r="B189" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C189" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
@@ -4182,13 +4194,13 @@
         <v>50</v>
       </c>
       <c r="B191" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C191" t="s">
         <v>51</v>
       </c>
       <c r="D191" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
@@ -4196,10 +4208,10 @@
         <v>50</v>
       </c>
       <c r="B192" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C192" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4207,10 +4219,10 @@
         <v>50</v>
       </c>
       <c r="B193" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C193" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4218,10 +4230,10 @@
         <v>50</v>
       </c>
       <c r="B194" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C194" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4229,10 +4241,10 @@
         <v>50</v>
       </c>
       <c r="B195" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C195" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4240,10 +4252,10 @@
         <v>50</v>
       </c>
       <c r="B196" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C196" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4251,10 +4263,10 @@
         <v>50</v>
       </c>
       <c r="B197" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C197" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4262,10 +4274,10 @@
         <v>50</v>
       </c>
       <c r="B198" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C198" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4273,10 +4285,10 @@
         <v>50</v>
       </c>
       <c r="B199" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C199" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4284,10 +4296,10 @@
         <v>50</v>
       </c>
       <c r="B200" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C200" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4295,10 +4307,10 @@
         <v>50</v>
       </c>
       <c r="B201" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C201" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4306,10 +4318,10 @@
         <v>50</v>
       </c>
       <c r="B202" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C202" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4317,10 +4329,10 @@
         <v>50</v>
       </c>
       <c r="B203" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C203" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4328,10 +4340,10 @@
         <v>50</v>
       </c>
       <c r="B204" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C204" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4339,10 +4351,10 @@
         <v>50</v>
       </c>
       <c r="B205" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C205" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4350,10 +4362,10 @@
         <v>50</v>
       </c>
       <c r="B206" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C206" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4361,10 +4373,10 @@
         <v>50</v>
       </c>
       <c r="B207" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C207" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4372,10 +4384,10 @@
         <v>50</v>
       </c>
       <c r="B208" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C208" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4383,10 +4395,10 @@
         <v>50</v>
       </c>
       <c r="B209" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C209" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4394,10 +4406,10 @@
         <v>50</v>
       </c>
       <c r="B210" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C210" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4405,10 +4417,10 @@
         <v>50</v>
       </c>
       <c r="B211" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C211" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4416,10 +4428,10 @@
         <v>50</v>
       </c>
       <c r="B212" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C212" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4427,10 +4439,10 @@
         <v>50</v>
       </c>
       <c r="B213" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C213" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4438,10 +4450,10 @@
         <v>50</v>
       </c>
       <c r="B214" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C214" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4449,10 +4461,10 @@
         <v>50</v>
       </c>
       <c r="B215" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C215" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4460,10 +4472,10 @@
         <v>50</v>
       </c>
       <c r="B216" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C216" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4471,10 +4483,10 @@
         <v>50</v>
       </c>
       <c r="B217" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C217" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4482,10 +4494,10 @@
         <v>50</v>
       </c>
       <c r="B218" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C218" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4493,10 +4505,10 @@
         <v>50</v>
       </c>
       <c r="B219" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C219" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4504,14 +4516,2391 @@
         <v>50</v>
       </c>
       <c r="B220" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C220" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17D1D00-0203-4AF7-89F9-FDB785A93226}">
+  <dimension ref="A1:D220"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>27</v>
+      </c>
+      <c r="B43" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>27</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>27</v>
+      </c>
+      <c r="B46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>27</v>
+      </c>
+      <c r="B49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>27</v>
+      </c>
+      <c r="B50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>27</v>
+      </c>
+      <c r="B51" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>27</v>
+      </c>
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>27</v>
+      </c>
+      <c r="B54" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>27</v>
+      </c>
+      <c r="B56" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>27</v>
+      </c>
+      <c r="B57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>27</v>
+      </c>
+      <c r="B58" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>27</v>
+      </c>
+      <c r="B59" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>27</v>
+      </c>
+      <c r="B60" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>27</v>
+      </c>
+      <c r="B61" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>27</v>
+      </c>
+      <c r="B62" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" t="s">
+        <v>51</v>
+      </c>
+      <c r="D64" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>39</v>
+      </c>
+      <c r="B68" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>39</v>
+      </c>
+      <c r="B69" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>39</v>
+      </c>
+      <c r="B70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>39</v>
+      </c>
+      <c r="B71" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>39</v>
+      </c>
+      <c r="B72" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>39</v>
+      </c>
+      <c r="B73" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>39</v>
+      </c>
+      <c r="B74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>39</v>
+      </c>
+      <c r="B75" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>39</v>
+      </c>
+      <c r="B76" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>39</v>
+      </c>
+      <c r="B78" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>39</v>
+      </c>
+      <c r="B79" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>39</v>
+      </c>
+      <c r="B80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>39</v>
+      </c>
+      <c r="B81" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>39</v>
+      </c>
+      <c r="B82" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>39</v>
+      </c>
+      <c r="B83" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>39</v>
+      </c>
+      <c r="B84" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>39</v>
+      </c>
+      <c r="B85" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>39</v>
+      </c>
+      <c r="B87" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>39</v>
+      </c>
+      <c r="B88" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>39</v>
+      </c>
+      <c r="B90" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>39</v>
+      </c>
+      <c r="B91" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>39</v>
+      </c>
+      <c r="B92" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>39</v>
+      </c>
+      <c r="B93" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>40</v>
+      </c>
+      <c r="B95" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" t="s">
+        <v>51</v>
+      </c>
+      <c r="D95" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>40</v>
+      </c>
+      <c r="B96" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>40</v>
+      </c>
+      <c r="B97" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>40</v>
+      </c>
+      <c r="B98" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>40</v>
+      </c>
+      <c r="B99" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>40</v>
+      </c>
+      <c r="B100" t="s">
+        <v>8</v>
+      </c>
+      <c r="C100" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>40</v>
+      </c>
+      <c r="B101" t="s">
+        <v>8</v>
+      </c>
+      <c r="C101" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>40</v>
+      </c>
+      <c r="B102" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>40</v>
+      </c>
+      <c r="B103" t="s">
+        <v>15</v>
+      </c>
+      <c r="C103" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>40</v>
+      </c>
+      <c r="B104" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>40</v>
+      </c>
+      <c r="B105" t="s">
+        <v>15</v>
+      </c>
+      <c r="C105" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>40</v>
+      </c>
+      <c r="B106" t="s">
+        <v>15</v>
+      </c>
+      <c r="C106" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>40</v>
+      </c>
+      <c r="B107" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>40</v>
+      </c>
+      <c r="B108" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>40</v>
+      </c>
+      <c r="B109" t="s">
+        <v>15</v>
+      </c>
+      <c r="C109" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>40</v>
+      </c>
+      <c r="B110" t="s">
+        <v>15</v>
+      </c>
+      <c r="C110" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>40</v>
+      </c>
+      <c r="B111" t="s">
+        <v>15</v>
+      </c>
+      <c r="C111" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>40</v>
+      </c>
+      <c r="B112" t="s">
+        <v>15</v>
+      </c>
+      <c r="C112" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>40</v>
+      </c>
+      <c r="B113" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>40</v>
+      </c>
+      <c r="B114" t="s">
+        <v>15</v>
+      </c>
+      <c r="C114" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>40</v>
+      </c>
+      <c r="B115" t="s">
+        <v>15</v>
+      </c>
+      <c r="C115" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>40</v>
+      </c>
+      <c r="B116" t="s">
+        <v>15</v>
+      </c>
+      <c r="C116" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>40</v>
+      </c>
+      <c r="B117" t="s">
+        <v>15</v>
+      </c>
+      <c r="C117" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>40</v>
+      </c>
+      <c r="B118" t="s">
+        <v>15</v>
+      </c>
+      <c r="C118" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>40</v>
+      </c>
+      <c r="B119" t="s">
+        <v>15</v>
+      </c>
+      <c r="C119" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>40</v>
+      </c>
+      <c r="B120" t="s">
+        <v>15</v>
+      </c>
+      <c r="C120" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>40</v>
+      </c>
+      <c r="B121" t="s">
+        <v>15</v>
+      </c>
+      <c r="C121" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>40</v>
+      </c>
+      <c r="B122" t="s">
+        <v>15</v>
+      </c>
+      <c r="C122" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>40</v>
+      </c>
+      <c r="B123" t="s">
+        <v>15</v>
+      </c>
+      <c r="C123" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>40</v>
+      </c>
+      <c r="B124" t="s">
+        <v>10</v>
+      </c>
+      <c r="C124" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>40</v>
+      </c>
+      <c r="B125" t="s">
+        <v>10</v>
+      </c>
+      <c r="C125" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>40</v>
+      </c>
+      <c r="B126" t="s">
+        <v>10</v>
+      </c>
+      <c r="C126" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>40</v>
+      </c>
+      <c r="B127" t="s">
+        <v>10</v>
+      </c>
+      <c r="C127" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>40</v>
+      </c>
+      <c r="B128" t="s">
+        <v>10</v>
+      </c>
+      <c r="C128" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>41</v>
+      </c>
+      <c r="B130" t="s">
+        <v>5</v>
+      </c>
+      <c r="C130" t="s">
+        <v>51</v>
+      </c>
+      <c r="D130" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>41</v>
+      </c>
+      <c r="B131" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>41</v>
+      </c>
+      <c r="B132" t="s">
+        <v>5</v>
+      </c>
+      <c r="C132" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>41</v>
+      </c>
+      <c r="B133" t="s">
+        <v>8</v>
+      </c>
+      <c r="C133" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>41</v>
+      </c>
+      <c r="B134" t="s">
+        <v>8</v>
+      </c>
+      <c r="C134" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>41</v>
+      </c>
+      <c r="B135" t="s">
+        <v>8</v>
+      </c>
+      <c r="C135" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>41</v>
+      </c>
+      <c r="B136" t="s">
+        <v>8</v>
+      </c>
+      <c r="C136" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>41</v>
+      </c>
+      <c r="B137" t="s">
+        <v>8</v>
+      </c>
+      <c r="C137" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>41</v>
+      </c>
+      <c r="B138" t="s">
+        <v>15</v>
+      </c>
+      <c r="C138" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>41</v>
+      </c>
+      <c r="B139" t="s">
+        <v>15</v>
+      </c>
+      <c r="C139" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>41</v>
+      </c>
+      <c r="B140" t="s">
+        <v>15</v>
+      </c>
+      <c r="C140" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>41</v>
+      </c>
+      <c r="B141" t="s">
+        <v>15</v>
+      </c>
+      <c r="C141" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>41</v>
+      </c>
+      <c r="B142" t="s">
+        <v>15</v>
+      </c>
+      <c r="C142" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>41</v>
+      </c>
+      <c r="B143" t="s">
+        <v>15</v>
+      </c>
+      <c r="C143" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>41</v>
+      </c>
+      <c r="B144" t="s">
+        <v>15</v>
+      </c>
+      <c r="C144" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>41</v>
+      </c>
+      <c r="B145" t="s">
+        <v>15</v>
+      </c>
+      <c r="C145" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>41</v>
+      </c>
+      <c r="B146" t="s">
+        <v>15</v>
+      </c>
+      <c r="C146" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>41</v>
+      </c>
+      <c r="B147" t="s">
+        <v>15</v>
+      </c>
+      <c r="C147" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>41</v>
+      </c>
+      <c r="B148" t="s">
+        <v>15</v>
+      </c>
+      <c r="C148" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>41</v>
+      </c>
+      <c r="B149" t="s">
+        <v>15</v>
+      </c>
+      <c r="C149" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>41</v>
+      </c>
+      <c r="B150" t="s">
+        <v>15</v>
+      </c>
+      <c r="C150" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>41</v>
+      </c>
+      <c r="B151" t="s">
+        <v>15</v>
+      </c>
+      <c r="C151" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>41</v>
+      </c>
+      <c r="B152" t="s">
+        <v>15</v>
+      </c>
+      <c r="C152" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>41</v>
+      </c>
+      <c r="B153" t="s">
+        <v>15</v>
+      </c>
+      <c r="C153" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>41</v>
+      </c>
+      <c r="B154" t="s">
+        <v>15</v>
+      </c>
+      <c r="C154" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>41</v>
+      </c>
+      <c r="B155" t="s">
+        <v>10</v>
+      </c>
+      <c r="C155" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>41</v>
+      </c>
+      <c r="B156" t="s">
+        <v>10</v>
+      </c>
+      <c r="C156" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>41</v>
+      </c>
+      <c r="B157" t="s">
+        <v>10</v>
+      </c>
+      <c r="C157" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>41</v>
+      </c>
+      <c r="B158" t="s">
+        <v>10</v>
+      </c>
+      <c r="C158" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>41</v>
+      </c>
+      <c r="B159" t="s">
+        <v>10</v>
+      </c>
+      <c r="C159" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>49</v>
+      </c>
+      <c r="B161" t="s">
+        <v>5</v>
+      </c>
+      <c r="C161" t="s">
+        <v>51</v>
+      </c>
+      <c r="D161" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>49</v>
+      </c>
+      <c r="B162" t="s">
+        <v>5</v>
+      </c>
+      <c r="C162" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>49</v>
+      </c>
+      <c r="B163" t="s">
+        <v>5</v>
+      </c>
+      <c r="C163" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>49</v>
+      </c>
+      <c r="B164" t="s">
+        <v>8</v>
+      </c>
+      <c r="C164" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>49</v>
+      </c>
+      <c r="B165" t="s">
+        <v>8</v>
+      </c>
+      <c r="C165" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>49</v>
+      </c>
+      <c r="B166" t="s">
+        <v>8</v>
+      </c>
+      <c r="C166" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>49</v>
+      </c>
+      <c r="B167" t="s">
+        <v>8</v>
+      </c>
+      <c r="C167" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>49</v>
+      </c>
+      <c r="B168" t="s">
+        <v>8</v>
+      </c>
+      <c r="C168" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>49</v>
+      </c>
+      <c r="B169" t="s">
+        <v>15</v>
+      </c>
+      <c r="C169" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>49</v>
+      </c>
+      <c r="B170" t="s">
+        <v>15</v>
+      </c>
+      <c r="C170" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>49</v>
+      </c>
+      <c r="B171" t="s">
+        <v>15</v>
+      </c>
+      <c r="C171" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>49</v>
+      </c>
+      <c r="B172" t="s">
+        <v>15</v>
+      </c>
+      <c r="C172" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>49</v>
+      </c>
+      <c r="B173" t="s">
+        <v>15</v>
+      </c>
+      <c r="C173" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>49</v>
+      </c>
+      <c r="B174" t="s">
+        <v>15</v>
+      </c>
+      <c r="C174" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>49</v>
+      </c>
+      <c r="B175" t="s">
+        <v>15</v>
+      </c>
+      <c r="C175" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>49</v>
+      </c>
+      <c r="B176" t="s">
+        <v>15</v>
+      </c>
+      <c r="C176" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>49</v>
+      </c>
+      <c r="B177" t="s">
+        <v>15</v>
+      </c>
+      <c r="C177" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>49</v>
+      </c>
+      <c r="B178" t="s">
+        <v>15</v>
+      </c>
+      <c r="C178" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>49</v>
+      </c>
+      <c r="B179" t="s">
+        <v>15</v>
+      </c>
+      <c r="C179" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>49</v>
+      </c>
+      <c r="B180" t="s">
+        <v>15</v>
+      </c>
+      <c r="C180" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>49</v>
+      </c>
+      <c r="B181" t="s">
+        <v>15</v>
+      </c>
+      <c r="C181" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>49</v>
+      </c>
+      <c r="B182" t="s">
+        <v>15</v>
+      </c>
+      <c r="C182" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>49</v>
+      </c>
+      <c r="B183" t="s">
+        <v>15</v>
+      </c>
+      <c r="C183" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>49</v>
+      </c>
+      <c r="B184" t="s">
+        <v>15</v>
+      </c>
+      <c r="C184" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>49</v>
+      </c>
+      <c r="B185" t="s">
+        <v>15</v>
+      </c>
+      <c r="C185" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>49</v>
+      </c>
+      <c r="B186" t="s">
+        <v>10</v>
+      </c>
+      <c r="C186" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>49</v>
+      </c>
+      <c r="B187" t="s">
+        <v>10</v>
+      </c>
+      <c r="C187" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>49</v>
+      </c>
+      <c r="B188" t="s">
+        <v>10</v>
+      </c>
+      <c r="C188" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>49</v>
+      </c>
+      <c r="B189" t="s">
+        <v>10</v>
+      </c>
+      <c r="C189" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>50</v>
+      </c>
+      <c r="B191" t="s">
+        <v>5</v>
+      </c>
+      <c r="C191" t="s">
+        <v>51</v>
+      </c>
+      <c r="D191" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>50</v>
+      </c>
+      <c r="B192" t="s">
+        <v>5</v>
+      </c>
+      <c r="C192" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>50</v>
+      </c>
+      <c r="B193" t="s">
+        <v>5</v>
+      </c>
+      <c r="C193" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>50</v>
+      </c>
+      <c r="B194" t="s">
+        <v>8</v>
+      </c>
+      <c r="C194" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>50</v>
+      </c>
+      <c r="B195" t="s">
+        <v>8</v>
+      </c>
+      <c r="C195" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>50</v>
+      </c>
+      <c r="B196" t="s">
+        <v>8</v>
+      </c>
+      <c r="C196" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>50</v>
+      </c>
+      <c r="B197" t="s">
+        <v>8</v>
+      </c>
+      <c r="C197" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>50</v>
+      </c>
+      <c r="B198" t="s">
+        <v>8</v>
+      </c>
+      <c r="C198" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>50</v>
+      </c>
+      <c r="B199" t="s">
+        <v>15</v>
+      </c>
+      <c r="C199" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>50</v>
+      </c>
+      <c r="B200" t="s">
+        <v>15</v>
+      </c>
+      <c r="C200" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>50</v>
+      </c>
+      <c r="B201" t="s">
+        <v>15</v>
+      </c>
+      <c r="C201" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>50</v>
+      </c>
+      <c r="B202" t="s">
+        <v>15</v>
+      </c>
+      <c r="C202" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>50</v>
+      </c>
+      <c r="B203" t="s">
+        <v>15</v>
+      </c>
+      <c r="C203" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>50</v>
+      </c>
+      <c r="B204" t="s">
+        <v>15</v>
+      </c>
+      <c r="C204" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>50</v>
+      </c>
+      <c r="B205" t="s">
+        <v>15</v>
+      </c>
+      <c r="C205" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>50</v>
+      </c>
+      <c r="B206" t="s">
+        <v>15</v>
+      </c>
+      <c r="C206" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>50</v>
+      </c>
+      <c r="B207" t="s">
+        <v>15</v>
+      </c>
+      <c r="C207" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>50</v>
+      </c>
+      <c r="B208" t="s">
+        <v>15</v>
+      </c>
+      <c r="C208" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>50</v>
+      </c>
+      <c r="B209" t="s">
+        <v>15</v>
+      </c>
+      <c r="C209" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>50</v>
+      </c>
+      <c r="B210" t="s">
+        <v>15</v>
+      </c>
+      <c r="C210" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>50</v>
+      </c>
+      <c r="B211" t="s">
+        <v>15</v>
+      </c>
+      <c r="C211" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>50</v>
+      </c>
+      <c r="B212" t="s">
+        <v>15</v>
+      </c>
+      <c r="C212" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>50</v>
+      </c>
+      <c r="B213" t="s">
+        <v>15</v>
+      </c>
+      <c r="C213" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>50</v>
+      </c>
+      <c r="B214" t="s">
+        <v>15</v>
+      </c>
+      <c r="C214" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>50</v>
+      </c>
+      <c r="B215" t="s">
+        <v>15</v>
+      </c>
+      <c r="C215" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>50</v>
+      </c>
+      <c r="B216" t="s">
+        <v>10</v>
+      </c>
+      <c r="C216" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>50</v>
+      </c>
+      <c r="B217" t="s">
+        <v>10</v>
+      </c>
+      <c r="C217" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>50</v>
+      </c>
+      <c r="B218" t="s">
+        <v>10</v>
+      </c>
+      <c r="C218" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>50</v>
+      </c>
+      <c r="B219" t="s">
+        <v>10</v>
+      </c>
+      <c r="C219" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>50</v>
+      </c>
+      <c r="B220" t="s">
+        <v>10</v>
+      </c>
+      <c r="C220" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/restaurant_menus.xlsx
+++ b/restaurant_menus.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ooredoomle-my.sharepoint.com/personal/ahmed_maail_ooredoo_mv/Documents/vishaal idea/ramadan menu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="11_F25DC773A252ABDACC1048D4395F6C085BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D047379-E370-4655-A106-07AAC918A408}"/>
+  <xr:revisionPtr revIDLastSave="357" documentId="11_F25DC773A252ABDACC1048D4395F6C085BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0BA42FB-0BF9-44AD-9594-6F31BFCFE162}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mamak" sheetId="1" r:id="rId1"/>
     <sheet name="citron" sheetId="2" r:id="rId2"/>
     <sheet name="pomelo" sheetId="3" r:id="rId3"/>
+    <sheet name="buruzu" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1839" uniqueCount="182">
   <si>
     <t>Day</t>
   </si>
@@ -410,6 +412,180 @@
   </si>
   <si>
     <t>Oreo Cheesecake</t>
+  </si>
+  <si>
+    <t>Roasted Pumpkin Soup</t>
+  </si>
+  <si>
+    <t>MVR 249+ PER PERSON</t>
+  </si>
+  <si>
+    <t>Steamed Rice</t>
+  </si>
+  <si>
+    <t>Chicken Pad Thai</t>
+  </si>
+  <si>
+    <t>Vegetable Pulao</t>
+  </si>
+  <si>
+    <t>Spaghetti Bolognaise</t>
+  </si>
+  <si>
+    <t>Chicken Cacciatore</t>
+  </si>
+  <si>
+    <t>Grilled Fish Fillet with</t>
+  </si>
+  <si>
+    <t>Lemon Butter Sauce</t>
+  </si>
+  <si>
+    <t>Roasted Zataar Potatoes</t>
+  </si>
+  <si>
+    <t>Steamed Vegetables</t>
+  </si>
+  <si>
+    <t>Eggplant Parmigiana</t>
+  </si>
+  <si>
+    <t>Valhomas &amp; Potato</t>
+  </si>
+  <si>
+    <t>Kirugarudhiya</t>
+  </si>
+  <si>
+    <t>Papadam</t>
+  </si>
+  <si>
+    <t>Fihunu Patties</t>
+  </si>
+  <si>
+    <t>Tuna Rolls</t>
+  </si>
+  <si>
+    <t>Kulhi Boakiba</t>
+  </si>
+  <si>
+    <t>Bashi Mashuni</t>
+  </si>
+  <si>
+    <t>Normal Mashuni</t>
+  </si>
+  <si>
+    <t>Maskurolhi</t>
+  </si>
+  <si>
+    <t>Fenfolhi</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Bruschetta Canape</t>
+  </si>
+  <si>
+    <t>Tuna Mousse Canape</t>
+  </si>
+  <si>
+    <t>Pizza Pinwheels</t>
+  </si>
+  <si>
+    <t>Faloodha</t>
+  </si>
+  <si>
+    <t>Fresh Mixed Fruit Juice</t>
+  </si>
+  <si>
+    <t>Grape packet juice</t>
+  </si>
+  <si>
+    <t>Mixed Omelet</t>
+  </si>
+  <si>
+    <t>Lamb Kofta Kebabs</t>
+  </si>
+  <si>
+    <t>(Tzatziki Sauce)</t>
+  </si>
+  <si>
+    <t>Garlic Roast Potatoes</t>
+  </si>
+  <si>
+    <t>Chicken Shawarma</t>
+  </si>
+  <si>
+    <t>Caesar with Tandoori</t>
+  </si>
+  <si>
+    <t>Brinjal Sambol</t>
+  </si>
+  <si>
+    <t>Hawaiian Salad</t>
+  </si>
+  <si>
+    <t>Freshly sliced</t>
+  </si>
+  <si>
+    <t>Cucumber &amp; Tomato</t>
+  </si>
+  <si>
+    <t>Strawberry Panna Cotta</t>
+  </si>
+  <si>
+    <t>Brownie Trifle</t>
+  </si>
+  <si>
+    <t>Chocolate Flan</t>
+  </si>
+  <si>
+    <t>Basbousa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dates </t>
+  </si>
+  <si>
+    <t>MVR 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">short eats </t>
+  </si>
+  <si>
+    <t>watermelon juice</t>
+  </si>
+  <si>
+    <t>ice coffee</t>
+  </si>
+  <si>
+    <t>roshi</t>
+  </si>
+  <si>
+    <t>barabo mas huni</t>
+  </si>
+  <si>
+    <t>parata</t>
+  </si>
+  <si>
+    <t>butterchicken</t>
+  </si>
+  <si>
+    <t>aisthu's chicken curry</t>
+  </si>
+  <si>
+    <t>mix omelette</t>
+  </si>
+  <si>
+    <t>gulab jamun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caramel pudding </t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>main dishes</t>
   </si>
 </sst>
 </file>
@@ -451,8 +627,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -734,13 +913,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D131"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -754,7 +933,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -768,7 +947,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -779,7 +958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -790,7 +969,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -801,7 +980,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -812,7 +991,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -823,7 +1002,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -834,7 +1013,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -845,7 +1024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -856,7 +1035,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -867,7 +1046,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -878,7 +1057,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -889,7 +1068,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -900,7 +1079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -911,7 +1090,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -922,7 +1101,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -933,7 +1112,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -944,7 +1123,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -955,7 +1134,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -969,7 +1148,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -980,7 +1159,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -991,7 +1170,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1002,7 +1181,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1013,7 +1192,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1024,7 +1203,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1035,7 +1214,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1046,7 +1225,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -1057,7 +1236,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -1068,7 +1247,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -1079,7 +1258,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -1090,7 +1269,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -1101,7 +1280,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -1112,7 +1291,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>27</v>
       </c>
@@ -1123,7 +1302,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -1134,7 +1313,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -1145,7 +1324,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -1159,7 +1338,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -1170,7 +1349,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -1181,7 +1360,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -1192,7 +1371,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>39</v>
       </c>
@@ -1203,7 +1382,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>39</v>
       </c>
@@ -1214,7 +1393,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>39</v>
       </c>
@@ -1225,7 +1404,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -1236,7 +1415,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>39</v>
       </c>
@@ -1247,7 +1426,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -1258,7 +1437,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>39</v>
       </c>
@@ -1269,7 +1448,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>39</v>
       </c>
@@ -1280,7 +1459,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>39</v>
       </c>
@@ -1291,7 +1470,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>39</v>
       </c>
@@ -1302,7 +1481,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -1313,7 +1492,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>39</v>
       </c>
@@ -1324,7 +1503,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>39</v>
       </c>
@@ -1335,7 +1514,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>39</v>
       </c>
@@ -1346,7 +1525,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>40</v>
       </c>
@@ -1360,7 +1539,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>40</v>
       </c>
@@ -1371,7 +1550,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>40</v>
       </c>
@@ -1382,7 +1561,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>40</v>
       </c>
@@ -1393,7 +1572,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>40</v>
       </c>
@@ -1404,7 +1583,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>40</v>
       </c>
@@ -1415,7 +1594,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>40</v>
       </c>
@@ -1426,7 +1605,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>40</v>
       </c>
@@ -1437,7 +1616,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>40</v>
       </c>
@@ -1448,7 +1627,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>40</v>
       </c>
@@ -1459,7 +1638,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>40</v>
       </c>
@@ -1470,7 +1649,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>40</v>
       </c>
@@ -1481,7 +1660,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>40</v>
       </c>
@@ -1492,7 +1671,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>40</v>
       </c>
@@ -1503,7 +1682,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>40</v>
       </c>
@@ -1514,7 +1693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>40</v>
       </c>
@@ -1525,7 +1704,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>40</v>
       </c>
@@ -1536,7 +1715,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>41</v>
       </c>
@@ -1550,7 +1729,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>41</v>
       </c>
@@ -1561,7 +1740,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>41</v>
       </c>
@@ -1572,7 +1751,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>41</v>
       </c>
@@ -1583,7 +1762,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>41</v>
       </c>
@@ -1594,7 +1773,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>41</v>
       </c>
@@ -1605,7 +1784,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>41</v>
       </c>
@@ -1616,7 +1795,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>41</v>
       </c>
@@ -1627,7 +1806,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>41</v>
       </c>
@@ -1638,7 +1817,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>41</v>
       </c>
@@ -1649,7 +1828,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>41</v>
       </c>
@@ -1660,7 +1839,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>41</v>
       </c>
@@ -1671,7 +1850,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>41</v>
       </c>
@@ -1682,7 +1861,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>41</v>
       </c>
@@ -1693,7 +1872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>41</v>
       </c>
@@ -1704,7 +1883,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>41</v>
       </c>
@@ -1715,7 +1894,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>41</v>
       </c>
@@ -1726,7 +1905,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>41</v>
       </c>
@@ -1737,7 +1916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>49</v>
       </c>
@@ -1751,7 +1930,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>49</v>
       </c>
@@ -1762,7 +1941,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>49</v>
       </c>
@@ -1773,7 +1952,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>49</v>
       </c>
@@ -1784,7 +1963,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>49</v>
       </c>
@@ -1795,7 +1974,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>49</v>
       </c>
@@ -1806,7 +1985,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>49</v>
       </c>
@@ -1817,7 +1996,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>49</v>
       </c>
@@ -1828,7 +2007,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>49</v>
       </c>
@@ -1839,7 +2018,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>49</v>
       </c>
@@ -1850,7 +2029,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>49</v>
       </c>
@@ -1861,7 +2040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>49</v>
       </c>
@@ -1872,7 +2051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>49</v>
       </c>
@@ -1883,7 +2062,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>49</v>
       </c>
@@ -1894,7 +2073,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>49</v>
       </c>
@@ -1905,7 +2084,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>49</v>
       </c>
@@ -1916,7 +2095,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>49</v>
       </c>
@@ -1927,7 +2106,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>49</v>
       </c>
@@ -1938,7 +2117,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>50</v>
       </c>
@@ -1952,7 +2131,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>50</v>
       </c>
@@ -1963,7 +2142,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>50</v>
       </c>
@@ -1974,7 +2153,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>50</v>
       </c>
@@ -1985,7 +2164,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>50</v>
       </c>
@@ -1996,7 +2175,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>50</v>
       </c>
@@ -2007,7 +2186,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>50</v>
       </c>
@@ -2018,7 +2197,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>50</v>
       </c>
@@ -2029,7 +2208,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>50</v>
       </c>
@@ -2040,7 +2219,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>50</v>
       </c>
@@ -2051,7 +2230,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>50</v>
       </c>
@@ -2062,7 +2241,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>50</v>
       </c>
@@ -2073,7 +2252,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>50</v>
       </c>
@@ -2084,7 +2263,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>50</v>
       </c>
@@ -2095,7 +2274,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>50</v>
       </c>
@@ -2106,7 +2285,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>50</v>
       </c>
@@ -2117,7 +2296,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>50</v>
       </c>
@@ -2128,7 +2307,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>50</v>
       </c>
@@ -2148,14 +2327,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958711E3-6C4F-4BD5-AB6C-48EB3BBDFE40}">
   <dimension ref="A1:D220"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2169,7 +2348,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2183,7 +2362,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2194,7 +2373,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2205,7 +2384,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2216,7 +2395,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2227,7 +2406,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -2238,7 +2417,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -2249,7 +2428,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -2260,7 +2439,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -2271,7 +2450,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -2282,7 +2461,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -2293,7 +2472,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -2304,7 +2483,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -2315,7 +2494,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -2326,7 +2505,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -2337,7 +2516,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -2348,7 +2527,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -2359,7 +2538,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -2370,7 +2549,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -2381,7 +2560,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -2392,7 +2571,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -2403,7 +2582,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -2414,7 +2593,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -2425,7 +2604,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -2436,7 +2615,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -2447,7 +2626,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -2458,7 +2637,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -2469,7 +2648,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -2480,7 +2659,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -2491,7 +2670,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -2502,7 +2681,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -2516,7 +2695,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>27</v>
       </c>
@@ -2527,7 +2706,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -2538,7 +2717,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -2549,7 +2728,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -2560,7 +2739,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -2571,7 +2750,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -2582,7 +2761,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -2593,7 +2772,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -2604,7 +2783,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -2615,7 +2794,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -2626,7 +2805,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -2637,7 +2816,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>27</v>
       </c>
@@ -2648,7 +2827,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>27</v>
       </c>
@@ -2659,7 +2838,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -2670,7 +2849,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>27</v>
       </c>
@@ -2681,7 +2860,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>27</v>
       </c>
@@ -2692,7 +2871,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>27</v>
       </c>
@@ -2703,7 +2882,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>27</v>
       </c>
@@ -2714,7 +2893,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>27</v>
       </c>
@@ -2725,7 +2904,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>27</v>
       </c>
@@ -2736,7 +2915,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>27</v>
       </c>
@@ -2747,7 +2926,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>27</v>
       </c>
@@ -2758,7 +2937,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>27</v>
       </c>
@@ -2769,7 +2948,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>27</v>
       </c>
@@ -2780,7 +2959,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>27</v>
       </c>
@@ -2791,7 +2970,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>27</v>
       </c>
@@ -2802,7 +2981,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>27</v>
       </c>
@@ -2813,7 +2992,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>27</v>
       </c>
@@ -2824,7 +3003,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -2838,7 +3017,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>39</v>
       </c>
@@ -2849,7 +3028,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>39</v>
       </c>
@@ -2860,7 +3039,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>39</v>
       </c>
@@ -2871,7 +3050,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>39</v>
       </c>
@@ -2882,7 +3061,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>39</v>
       </c>
@@ -2893,7 +3072,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>39</v>
       </c>
@@ -2904,7 +3083,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>39</v>
       </c>
@@ -2915,7 +3094,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>39</v>
       </c>
@@ -2926,7 +3105,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>39</v>
       </c>
@@ -2937,7 +3116,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>39</v>
       </c>
@@ -2948,7 +3127,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>39</v>
       </c>
@@ -2959,7 +3138,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>39</v>
       </c>
@@ -2970,7 +3149,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>39</v>
       </c>
@@ -2981,7 +3160,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>39</v>
       </c>
@@ -2992,7 +3171,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>39</v>
       </c>
@@ -3003,7 +3182,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>39</v>
       </c>
@@ -3014,7 +3193,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>39</v>
       </c>
@@ -3025,7 +3204,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>39</v>
       </c>
@@ -3036,7 +3215,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>39</v>
       </c>
@@ -3047,7 +3226,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>39</v>
       </c>
@@ -3058,7 +3237,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>39</v>
       </c>
@@ -3069,7 +3248,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>39</v>
       </c>
@@ -3080,7 +3259,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>39</v>
       </c>
@@ -3091,7 +3270,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>39</v>
       </c>
@@ -3102,7 +3281,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>39</v>
       </c>
@@ -3113,7 +3292,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>39</v>
       </c>
@@ -3124,7 +3303,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>39</v>
       </c>
@@ -3135,7 +3314,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>39</v>
       </c>
@@ -3146,7 +3325,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>39</v>
       </c>
@@ -3157,7 +3336,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>40</v>
       </c>
@@ -3171,7 +3350,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>40</v>
       </c>
@@ -3182,7 +3361,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>40</v>
       </c>
@@ -3193,7 +3372,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -3204,7 +3383,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>40</v>
       </c>
@@ -3215,7 +3394,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -3226,7 +3405,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>40</v>
       </c>
@@ -3237,7 +3416,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -3248,7 +3427,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -3259,7 +3438,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -3270,7 +3449,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>40</v>
       </c>
@@ -3281,7 +3460,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>40</v>
       </c>
@@ -3292,7 +3471,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -3303,7 +3482,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>40</v>
       </c>
@@ -3314,7 +3493,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>40</v>
       </c>
@@ -3325,7 +3504,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>40</v>
       </c>
@@ -3336,7 +3515,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>40</v>
       </c>
@@ -3347,7 +3526,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>40</v>
       </c>
@@ -3358,7 +3537,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -3369,7 +3548,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>40</v>
       </c>
@@ -3380,7 +3559,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>40</v>
       </c>
@@ -3391,7 +3570,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>40</v>
       </c>
@@ -3402,7 +3581,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>40</v>
       </c>
@@ -3413,7 +3592,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>40</v>
       </c>
@@ -3424,7 +3603,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>40</v>
       </c>
@@ -3435,7 +3614,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>40</v>
       </c>
@@ -3446,7 +3625,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>40</v>
       </c>
@@ -3457,7 +3636,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>40</v>
       </c>
@@ -3468,7 +3647,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>40</v>
       </c>
@@ -3479,7 +3658,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>40</v>
       </c>
@@ -3490,7 +3669,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>40</v>
       </c>
@@ -3501,7 +3680,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>40</v>
       </c>
@@ -3512,7 +3691,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>40</v>
       </c>
@@ -3523,7 +3702,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>40</v>
       </c>
@@ -3534,7 +3713,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>41</v>
       </c>
@@ -3548,7 +3727,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>41</v>
       </c>
@@ -3559,7 +3738,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>41</v>
       </c>
@@ -3570,7 +3749,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>41</v>
       </c>
@@ -3581,7 +3760,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>41</v>
       </c>
@@ -3592,7 +3771,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>41</v>
       </c>
@@ -3603,7 +3782,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>41</v>
       </c>
@@ -3614,7 +3793,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>41</v>
       </c>
@@ -3625,7 +3804,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>41</v>
       </c>
@@ -3636,7 +3815,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>41</v>
       </c>
@@ -3647,7 +3826,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>41</v>
       </c>
@@ -3658,7 +3837,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>41</v>
       </c>
@@ -3669,7 +3848,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>41</v>
       </c>
@@ -3680,7 +3859,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>41</v>
       </c>
@@ -3691,7 +3870,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>41</v>
       </c>
@@ -3702,7 +3881,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>41</v>
       </c>
@@ -3713,7 +3892,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>41</v>
       </c>
@@ -3724,7 +3903,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>41</v>
       </c>
@@ -3735,7 +3914,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>41</v>
       </c>
@@ -3746,7 +3925,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>41</v>
       </c>
@@ -3757,7 +3936,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>41</v>
       </c>
@@ -3768,7 +3947,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>41</v>
       </c>
@@ -3779,7 +3958,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>41</v>
       </c>
@@ -3790,7 +3969,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>41</v>
       </c>
@@ -3801,7 +3980,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>41</v>
       </c>
@@ -3812,7 +3991,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>41</v>
       </c>
@@ -3823,7 +4002,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>41</v>
       </c>
@@ -3834,7 +4013,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>41</v>
       </c>
@@ -3845,7 +4024,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>41</v>
       </c>
@@ -3856,7 +4035,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>41</v>
       </c>
@@ -3867,7 +4046,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>49</v>
       </c>
@@ -3881,7 +4060,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>49</v>
       </c>
@@ -3892,7 +4071,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>49</v>
       </c>
@@ -3903,7 +4082,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>49</v>
       </c>
@@ -3914,7 +4093,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>49</v>
       </c>
@@ -3925,7 +4104,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>49</v>
       </c>
@@ -3936,7 +4115,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>49</v>
       </c>
@@ -3947,7 +4126,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>49</v>
       </c>
@@ -3958,7 +4137,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>49</v>
       </c>
@@ -3969,7 +4148,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>49</v>
       </c>
@@ -3980,7 +4159,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>49</v>
       </c>
@@ -3991,7 +4170,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>49</v>
       </c>
@@ -4002,7 +4181,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>49</v>
       </c>
@@ -4013,7 +4192,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>49</v>
       </c>
@@ -4024,7 +4203,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>49</v>
       </c>
@@ -4035,7 +4214,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>49</v>
       </c>
@@ -4046,7 +4225,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>49</v>
       </c>
@@ -4057,7 +4236,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>49</v>
       </c>
@@ -4068,7 +4247,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>49</v>
       </c>
@@ -4079,7 +4258,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>49</v>
       </c>
@@ -4090,7 +4269,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>49</v>
       </c>
@@ -4101,7 +4280,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>49</v>
       </c>
@@ -4112,7 +4291,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>49</v>
       </c>
@@ -4123,7 +4302,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>49</v>
       </c>
@@ -4134,7 +4313,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>49</v>
       </c>
@@ -4145,7 +4324,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>49</v>
       </c>
@@ -4156,7 +4335,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>49</v>
       </c>
@@ -4167,7 +4346,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>49</v>
       </c>
@@ -4178,7 +4357,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>49</v>
       </c>
@@ -4189,7 +4368,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>50</v>
       </c>
@@ -4203,7 +4382,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>50</v>
       </c>
@@ -4214,7 +4393,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>50</v>
       </c>
@@ -4225,7 +4404,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>50</v>
       </c>
@@ -4236,7 +4415,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>50</v>
       </c>
@@ -4247,7 +4426,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>50</v>
       </c>
@@ -4258,7 +4437,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>50</v>
       </c>
@@ -4269,7 +4448,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>50</v>
       </c>
@@ -4280,7 +4459,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>50</v>
       </c>
@@ -4291,7 +4470,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>50</v>
       </c>
@@ -4302,7 +4481,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>50</v>
       </c>
@@ -4313,7 +4492,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>50</v>
       </c>
@@ -4324,7 +4503,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>50</v>
       </c>
@@ -4335,7 +4514,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>50</v>
       </c>
@@ -4346,7 +4525,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>50</v>
       </c>
@@ -4357,7 +4536,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>50</v>
       </c>
@@ -4368,7 +4547,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>50</v>
       </c>
@@ -4379,7 +4558,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>50</v>
       </c>
@@ -4390,7 +4569,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>50</v>
       </c>
@@ -4401,7 +4580,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>50</v>
       </c>
@@ -4412,7 +4591,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>50</v>
       </c>
@@ -4423,7 +4602,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>50</v>
       </c>
@@ -4434,7 +4613,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>50</v>
       </c>
@@ -4445,7 +4624,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>50</v>
       </c>
@@ -4456,7 +4635,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>50</v>
       </c>
@@ -4467,7 +4646,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>50</v>
       </c>
@@ -4478,7 +4657,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>50</v>
       </c>
@@ -4489,7 +4668,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>50</v>
       </c>
@@ -4500,7 +4679,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>50</v>
       </c>
@@ -4511,7 +4690,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>50</v>
       </c>
@@ -4531,9 +4710,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17D1D00-0203-4AF7-89F9-FDB785A93226}">
   <dimension ref="A1:D220"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4547,7 +4726,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -4561,7 +4740,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -4572,7 +4751,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4583,7 +4762,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4594,7 +4773,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -4605,7 +4784,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -4616,7 +4795,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -4627,7 +4806,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -4638,7 +4817,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -4649,7 +4828,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -4660,7 +4839,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -4671,7 +4850,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -4682,7 +4861,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -4693,7 +4872,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -4704,7 +4883,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -4715,7 +4894,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -4726,7 +4905,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -4737,7 +4916,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -4748,7 +4927,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -4759,7 +4938,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -4770,7 +4949,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -4781,7 +4960,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -4792,7 +4971,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -4803,7 +4982,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -4814,7 +4993,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -4825,7 +5004,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -4836,7 +5015,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -4847,7 +5026,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -4858,7 +5037,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -4869,7 +5048,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -4880,7 +5059,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -4894,7 +5073,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>27</v>
       </c>
@@ -4905,7 +5084,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -4916,7 +5095,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -4927,7 +5106,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -4938,7 +5117,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -4949,7 +5128,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -4960,7 +5139,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -4971,7 +5150,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -4982,7 +5161,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -4993,7 +5172,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -5004,7 +5183,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -5015,7 +5194,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>27</v>
       </c>
@@ -5026,7 +5205,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>27</v>
       </c>
@@ -5037,7 +5216,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -5048,7 +5227,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>27</v>
       </c>
@@ -5059,7 +5238,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>27</v>
       </c>
@@ -5070,7 +5249,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>27</v>
       </c>
@@ -5081,7 +5260,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>27</v>
       </c>
@@ -5092,7 +5271,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>27</v>
       </c>
@@ -5103,7 +5282,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>27</v>
       </c>
@@ -5114,7 +5293,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>27</v>
       </c>
@@ -5125,7 +5304,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>27</v>
       </c>
@@ -5136,7 +5315,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>27</v>
       </c>
@@ -5147,7 +5326,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>27</v>
       </c>
@@ -5158,7 +5337,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>27</v>
       </c>
@@ -5169,7 +5348,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>27</v>
       </c>
@@ -5180,7 +5359,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>27</v>
       </c>
@@ -5191,7 +5370,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>27</v>
       </c>
@@ -5202,7 +5381,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -5216,7 +5395,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>39</v>
       </c>
@@ -5227,7 +5406,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>39</v>
       </c>
@@ -5238,7 +5417,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>39</v>
       </c>
@@ -5249,7 +5428,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>39</v>
       </c>
@@ -5260,7 +5439,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>39</v>
       </c>
@@ -5271,7 +5450,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>39</v>
       </c>
@@ -5282,7 +5461,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>39</v>
       </c>
@@ -5293,7 +5472,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>39</v>
       </c>
@@ -5304,7 +5483,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>39</v>
       </c>
@@ -5315,7 +5494,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>39</v>
       </c>
@@ -5326,7 +5505,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>39</v>
       </c>
@@ -5337,7 +5516,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>39</v>
       </c>
@@ -5348,7 +5527,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>39</v>
       </c>
@@ -5359,7 +5538,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>39</v>
       </c>
@@ -5370,7 +5549,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>39</v>
       </c>
@@ -5381,7 +5560,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>39</v>
       </c>
@@ -5392,7 +5571,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>39</v>
       </c>
@@ -5403,7 +5582,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>39</v>
       </c>
@@ -5414,7 +5593,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>39</v>
       </c>
@@ -5425,7 +5604,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>39</v>
       </c>
@@ -5436,7 +5615,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>39</v>
       </c>
@@ -5447,7 +5626,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>39</v>
       </c>
@@ -5458,7 +5637,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>39</v>
       </c>
@@ -5469,7 +5648,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>39</v>
       </c>
@@ -5480,7 +5659,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>39</v>
       </c>
@@ -5491,7 +5670,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>39</v>
       </c>
@@ -5502,7 +5681,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>39</v>
       </c>
@@ -5513,7 +5692,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>39</v>
       </c>
@@ -5524,7 +5703,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>39</v>
       </c>
@@ -5535,7 +5714,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>40</v>
       </c>
@@ -5549,7 +5728,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>40</v>
       </c>
@@ -5560,7 +5739,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>40</v>
       </c>
@@ -5571,7 +5750,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -5582,7 +5761,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>40</v>
       </c>
@@ -5593,7 +5772,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -5604,7 +5783,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>40</v>
       </c>
@@ -5615,7 +5794,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -5626,7 +5805,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -5637,7 +5816,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -5648,7 +5827,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>40</v>
       </c>
@@ -5659,7 +5838,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>40</v>
       </c>
@@ -5670,7 +5849,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -5681,7 +5860,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>40</v>
       </c>
@@ -5692,7 +5871,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>40</v>
       </c>
@@ -5703,7 +5882,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>40</v>
       </c>
@@ -5714,7 +5893,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>40</v>
       </c>
@@ -5725,7 +5904,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>40</v>
       </c>
@@ -5736,7 +5915,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -5747,7 +5926,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>40</v>
       </c>
@@ -5758,7 +5937,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>40</v>
       </c>
@@ -5769,7 +5948,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>40</v>
       </c>
@@ -5780,7 +5959,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>40</v>
       </c>
@@ -5791,7 +5970,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>40</v>
       </c>
@@ -5802,7 +5981,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>40</v>
       </c>
@@ -5813,7 +5992,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>40</v>
       </c>
@@ -5824,7 +6003,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>40</v>
       </c>
@@ -5835,7 +6014,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>40</v>
       </c>
@@ -5846,7 +6025,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>40</v>
       </c>
@@ -5857,7 +6036,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>40</v>
       </c>
@@ -5868,7 +6047,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>40</v>
       </c>
@@ -5879,7 +6058,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>40</v>
       </c>
@@ -5890,7 +6069,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>40</v>
       </c>
@@ -5901,7 +6080,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>40</v>
       </c>
@@ -5912,7 +6091,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>41</v>
       </c>
@@ -5926,7 +6105,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>41</v>
       </c>
@@ -5937,7 +6116,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>41</v>
       </c>
@@ -5948,7 +6127,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>41</v>
       </c>
@@ -5959,7 +6138,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>41</v>
       </c>
@@ -5970,7 +6149,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>41</v>
       </c>
@@ -5981,7 +6160,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>41</v>
       </c>
@@ -5992,7 +6171,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>41</v>
       </c>
@@ -6003,7 +6182,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>41</v>
       </c>
@@ -6014,7 +6193,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>41</v>
       </c>
@@ -6025,7 +6204,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>41</v>
       </c>
@@ -6036,7 +6215,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>41</v>
       </c>
@@ -6047,7 +6226,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>41</v>
       </c>
@@ -6058,7 +6237,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>41</v>
       </c>
@@ -6069,7 +6248,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>41</v>
       </c>
@@ -6080,7 +6259,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>41</v>
       </c>
@@ -6091,7 +6270,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>41</v>
       </c>
@@ -6102,7 +6281,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>41</v>
       </c>
@@ -6113,7 +6292,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>41</v>
       </c>
@@ -6124,7 +6303,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>41</v>
       </c>
@@ -6135,7 +6314,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>41</v>
       </c>
@@ -6146,7 +6325,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>41</v>
       </c>
@@ -6157,7 +6336,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>41</v>
       </c>
@@ -6168,7 +6347,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>41</v>
       </c>
@@ -6179,7 +6358,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>41</v>
       </c>
@@ -6190,7 +6369,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>41</v>
       </c>
@@ -6201,7 +6380,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>41</v>
       </c>
@@ -6212,7 +6391,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>41</v>
       </c>
@@ -6223,7 +6402,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>41</v>
       </c>
@@ -6234,7 +6413,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>41</v>
       </c>
@@ -6245,7 +6424,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>49</v>
       </c>
@@ -6259,7 +6438,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>49</v>
       </c>
@@ -6270,7 +6449,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>49</v>
       </c>
@@ -6281,7 +6460,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>49</v>
       </c>
@@ -6292,7 +6471,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>49</v>
       </c>
@@ -6303,7 +6482,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>49</v>
       </c>
@@ -6314,7 +6493,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>49</v>
       </c>
@@ -6325,7 +6504,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>49</v>
       </c>
@@ -6336,7 +6515,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>49</v>
       </c>
@@ -6347,7 +6526,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>49</v>
       </c>
@@ -6358,7 +6537,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>49</v>
       </c>
@@ -6369,7 +6548,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>49</v>
       </c>
@@ -6380,7 +6559,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>49</v>
       </c>
@@ -6391,7 +6570,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>49</v>
       </c>
@@ -6402,7 +6581,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>49</v>
       </c>
@@ -6413,7 +6592,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>49</v>
       </c>
@@ -6424,7 +6603,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>49</v>
       </c>
@@ -6435,7 +6614,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>49</v>
       </c>
@@ -6446,7 +6625,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>49</v>
       </c>
@@ -6457,7 +6636,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>49</v>
       </c>
@@ -6468,7 +6647,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>49</v>
       </c>
@@ -6479,7 +6658,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>49</v>
       </c>
@@ -6490,7 +6669,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>49</v>
       </c>
@@ -6501,7 +6680,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>49</v>
       </c>
@@ -6512,7 +6691,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>49</v>
       </c>
@@ -6523,7 +6702,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>49</v>
       </c>
@@ -6534,7 +6713,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>49</v>
       </c>
@@ -6545,7 +6724,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>49</v>
       </c>
@@ -6556,7 +6735,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>49</v>
       </c>
@@ -6567,7 +6746,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>50</v>
       </c>
@@ -6581,7 +6760,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>50</v>
       </c>
@@ -6592,7 +6771,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>50</v>
       </c>
@@ -6603,7 +6782,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>50</v>
       </c>
@@ -6614,7 +6793,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>50</v>
       </c>
@@ -6625,7 +6804,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>50</v>
       </c>
@@ -6636,7 +6815,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>50</v>
       </c>
@@ -6647,7 +6826,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>50</v>
       </c>
@@ -6658,7 +6837,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>50</v>
       </c>
@@ -6669,7 +6848,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>50</v>
       </c>
@@ -6680,7 +6859,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>50</v>
       </c>
@@ -6691,7 +6870,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>50</v>
       </c>
@@ -6702,7 +6881,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>50</v>
       </c>
@@ -6713,7 +6892,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>50</v>
       </c>
@@ -6724,7 +6903,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>50</v>
       </c>
@@ -6735,7 +6914,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>50</v>
       </c>
@@ -6746,7 +6925,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>50</v>
       </c>
@@ -6757,7 +6936,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>50</v>
       </c>
@@ -6768,7 +6947,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>50</v>
       </c>
@@ -6779,7 +6958,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>50</v>
       </c>
@@ -6790,7 +6969,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>50</v>
       </c>
@@ -6801,7 +6980,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>50</v>
       </c>
@@ -6812,7 +6991,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>50</v>
       </c>
@@ -6823,7 +7002,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>50</v>
       </c>
@@ -6834,7 +7013,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>50</v>
       </c>
@@ -6845,7 +7024,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>50</v>
       </c>
@@ -6856,7 +7035,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>50</v>
       </c>
@@ -6867,7 +7046,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>50</v>
       </c>
@@ -6878,7 +7057,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>50</v>
       </c>
@@ -6889,7 +7068,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>50</v>
       </c>
@@ -6898,6 +7077,671 @@
       </c>
       <c r="C220" t="s">
         <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96E5C589-12B6-46D0-ACA0-F15124B14248}">
+  <dimension ref="A1:D49"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>181</v>
+      </c>
+      <c r="C16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" t="s">
+        <v>181</v>
+      </c>
+      <c r="C17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s">
+        <v>181</v>
+      </c>
+      <c r="C20" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" t="s">
+        <v>166</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64ED07A9-2F73-4233-8727-B6937003F0D4}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/restaurant_menus.xlsx
+++ b/restaurant_menus.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ooredoomle-my.sharepoint.com/personal/ahmed_maail_ooredoo_mv/Documents/vishaal idea/ramadan menu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="357" documentId="11_F25DC773A252ABDACC1048D4395F6C085BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0BA42FB-0BF9-44AD-9594-6F31BFCFE162}"/>
+  <xr:revisionPtr revIDLastSave="466" documentId="11_F25DC773A252ABDACC1048D4395F6C085BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AC237CA-34C0-41AA-91C3-DF74B507E2A3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mamak" sheetId="1" r:id="rId1"/>
     <sheet name="citron" sheetId="2" r:id="rId2"/>
     <sheet name="pomelo" sheetId="3" r:id="rId3"/>
     <sheet name="buruzu" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
+    <sheet name="house of flavors" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1839" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2300" uniqueCount="301">
   <si>
     <t>Day</t>
   </si>
@@ -414,6 +415,9 @@
     <t>Oreo Cheesecake</t>
   </si>
   <si>
+    <t>main dishes</t>
+  </si>
+  <si>
     <t>Roasted Pumpkin Soup</t>
   </si>
   <si>
@@ -585,14 +589,368 @@
     <t>water</t>
   </si>
   <si>
-    <t>main dishes</t>
+    <t>Short Eats</t>
+  </si>
+  <si>
+    <t>Ice Coffee</t>
+  </si>
+  <si>
+    <t>Tuna Mas Huni</t>
+  </si>
+  <si>
+    <t>Chicken Alfredo Pasta</t>
+  </si>
+  <si>
+    <t>Aisthu's Chicken Curry</t>
+  </si>
+  <si>
+    <t>Mix Omelette</t>
+  </si>
+  <si>
+    <t>Pirini</t>
+  </si>
+  <si>
+    <t>Caramel Pudding</t>
+  </si>
+  <si>
+    <t>Orange Juice</t>
+  </si>
+  <si>
+    <t>Barabo Mas Huni</t>
+  </si>
+  <si>
+    <t>Spagetti Aglio Olio</t>
+  </si>
+  <si>
+    <t>Deviled Sausage</t>
+  </si>
+  <si>
+    <t>Mas Riha</t>
+  </si>
+  <si>
+    <t>Fruit Cocktail</t>
+  </si>
+  <si>
+    <t>Barabo Massuni</t>
+  </si>
+  <si>
+    <t>Vegetable Fried Rice</t>
+  </si>
+  <si>
+    <t>Kulhimas</t>
+  </si>
+  <si>
+    <t>Dhon Riha</t>
+  </si>
+  <si>
+    <t>Fruit Custard</t>
+  </si>
+  <si>
+    <t>Wok Fried Tuna Rice</t>
+  </si>
+  <si>
+    <t>Chilli Fish</t>
+  </si>
+  <si>
+    <t>Mixed Fruit Juice</t>
+  </si>
+  <si>
+    <t>Faiy Mas Huni</t>
+  </si>
+  <si>
+    <t>Garlic Rice</t>
+  </si>
+  <si>
+    <t>Devilled Chicken</t>
+  </si>
+  <si>
+    <t>Chicken Biriyani</t>
+  </si>
+  <si>
+    <t>Raita</t>
+  </si>
+  <si>
+    <t>Aloo Gobi</t>
+  </si>
+  <si>
+    <t>Karaafani</t>
+  </si>
+  <si>
+    <t>Caesar Salad</t>
+  </si>
+  <si>
+    <t>Greek Salad</t>
+  </si>
+  <si>
+    <t>Roshi &amp; Battura</t>
+  </si>
+  <si>
+    <t>Mongolian Fried Rice</t>
+  </si>
+  <si>
+    <t>Penne Alfredo</t>
+  </si>
+  <si>
+    <t>Mustard Honey Chicken</t>
+  </si>
+  <si>
+    <t>Kan Kun Beef</t>
+  </si>
+  <si>
+    <t>Kulhi Mas</t>
+  </si>
+  <si>
+    <t>Aalu Gobi</t>
+  </si>
+  <si>
+    <t>Vegetable Chopsuey</t>
+  </si>
+  <si>
+    <t>Omaali</t>
+  </si>
+  <si>
+    <t>Blueberry Cheesecake</t>
+  </si>
+  <si>
+    <t>Assorted Fresh Fruits</t>
+  </si>
+  <si>
+    <t>Tea or Coffee</t>
+  </si>
+  <si>
+    <t>Water &amp; Nuts</t>
+  </si>
+  <si>
+    <t>Passionfruit Juice</t>
+  </si>
+  <si>
+    <t>Green Salad</t>
+  </si>
+  <si>
+    <t>Roshi &amp; Fen Folhi</t>
+  </si>
+  <si>
+    <t>Macaroni Carbonara</t>
+  </si>
+  <si>
+    <t>Tandoori Chicken</t>
+  </si>
+  <si>
+    <t>Beef Bulgogi</t>
+  </si>
+  <si>
+    <t>Kandu Kukulhu</t>
+  </si>
+  <si>
+    <t>Sri Lankan Devilled Potato</t>
+  </si>
+  <si>
+    <t>Vegetable Manchurian</t>
+  </si>
+  <si>
+    <t>***************</t>
+  </si>
+  <si>
+    <t>Passion Fruit Mousse</t>
+  </si>
+  <si>
+    <t>Tiramisu Cake</t>
+  </si>
+  <si>
+    <t>Sweet Filling</t>
+  </si>
+  <si>
+    <t>Refreshments</t>
+  </si>
+  <si>
+    <t>大大火大大大大大大文大大大大大</t>
+  </si>
+  <si>
+    <t>Salads</t>
+  </si>
+  <si>
+    <t>Bashi Mas Huni</t>
+  </si>
+  <si>
+    <t>Chinese Fried Rice</t>
+  </si>
+  <si>
+    <t>Spaghetti Melanzane</t>
+  </si>
+  <si>
+    <t>Boot Stoganirt</t>
+  </si>
+  <si>
+    <t>Lebanese Grilled Chicken</t>
+  </si>
+  <si>
+    <t>HanaaKuri Mas</t>
+  </si>
+  <si>
+    <t>Tempered Potato</t>
+  </si>
+  <si>
+    <t>Cinnamon Cake with Ganache</t>
+  </si>
+  <si>
+    <t>Fruit Gateaux</t>
+  </si>
+  <si>
+    <t>Cheese Cake</t>
+  </si>
+  <si>
+    <t>*火大大大火大大大火大火大大大</t>
+  </si>
+  <si>
+    <t>Mango Juice</t>
+  </si>
+  <si>
+    <t>Thai Beef Salad</t>
+  </si>
+  <si>
+    <t>Roshi &amp; Fenfolhi</t>
+  </si>
+  <si>
+    <t>Spinach Fried Rice</t>
+  </si>
+  <si>
+    <t>Penne Alla Rustica</t>
+  </si>
+  <si>
+    <t>Chicken Tikka Masala</t>
+  </si>
+  <si>
+    <t>Lebanese Beef Kebab</t>
+  </si>
+  <si>
+    <t>Hanaakuri Mas</t>
+  </si>
+  <si>
+    <t>Hungarian Potato</t>
+  </si>
+  <si>
+    <t>Sauteed Vegetables</t>
+  </si>
+  <si>
+    <t>"******t"**</t>
+  </si>
+  <si>
+    <t>Le Lait Gateau</t>
+  </si>
+  <si>
+    <t>Cheese Cakae</t>
+  </si>
+  <si>
+    <t>Guava Juice</t>
+  </si>
+  <si>
+    <t>*************★*</t>
+  </si>
+  <si>
+    <t>American Salad</t>
+  </si>
+  <si>
+    <t>Maldivian Tuna Salad</t>
+  </si>
+  <si>
+    <t>Roshi &amp; Paratta</t>
+  </si>
+  <si>
+    <t>Manchurian Fried Rice</t>
+  </si>
+  <si>
+    <t>Spaghetti Bolognese</t>
+  </si>
+  <si>
+    <t>Alfaham Chicken</t>
+  </si>
+  <si>
+    <t>Srilankan Beef Curry</t>
+  </si>
+  <si>
+    <t>Grilled Fish Lemon Butter</t>
+  </si>
+  <si>
+    <t>Vegetable Au Gratin</t>
+  </si>
+  <si>
+    <t>**************</t>
+  </si>
+  <si>
+    <t>Kiwi Gateaux</t>
+  </si>
+  <si>
+    <t>Sweet Fling</t>
+  </si>
+  <si>
+    <t>Karaafani®</t>
+  </si>
+  <si>
+    <t>Thai Chicken Salad</t>
+  </si>
+  <si>
+    <t>Roshi &amp; Yeast Roshi</t>
+  </si>
+  <si>
+    <t>Sweet Corn &amp; Sultan Rice</t>
+  </si>
+  <si>
+    <t>Penne Alla Salsa Rosa</t>
+  </si>
+  <si>
+    <t>Tandoori Shish Kebab</t>
+  </si>
+  <si>
+    <t>Mongolian Beef</t>
+  </si>
+  <si>
+    <t>Musamma Curry</t>
+  </si>
+  <si>
+    <t>Aubergine Provencal</t>
+  </si>
+  <si>
+    <t>***%**********</t>
+  </si>
+  <si>
+    <t>Chocolate Mousse</t>
+  </si>
+  <si>
+    <t>Kesari</t>
+  </si>
+  <si>
+    <t>New York Cheesecake</t>
+  </si>
+  <si>
+    <t>****★**********</t>
+  </si>
+  <si>
+    <t>Florist Green Salad</t>
+  </si>
+  <si>
+    <t>Mixed Vegetable Pulao</t>
+  </si>
+  <si>
+    <t>Spaghetti Aglio Olio</t>
+  </si>
+  <si>
+    <t>Lebanese Chicken</t>
+  </si>
+  <si>
+    <t>Deviled Fish</t>
+  </si>
+  <si>
+    <t>**********w</t>
+  </si>
+  <si>
+    <t>Cinnamon Chocolate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -602,6 +960,19 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="18"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -627,9 +998,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -913,13 +1290,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D131"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -933,7 +1310,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -947,7 +1324,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -958,7 +1335,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -969,7 +1346,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -980,7 +1357,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -991,7 +1368,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1002,7 +1379,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1013,7 +1390,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1024,7 +1401,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1035,7 +1412,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1046,7 +1423,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1057,7 +1434,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1068,7 +1445,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1079,7 +1456,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1090,7 +1467,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1101,7 +1478,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1112,7 +1489,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1123,7 +1500,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1134,7 +1511,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -1148,7 +1525,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -1159,7 +1536,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1170,7 +1547,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1181,7 +1558,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1192,7 +1569,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1203,7 +1580,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1214,7 +1591,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1225,7 +1602,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -1236,7 +1613,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -1247,7 +1624,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -1258,7 +1635,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -1269,7 +1646,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -1280,7 +1657,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -1291,7 +1668,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>27</v>
       </c>
@@ -1302,7 +1679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -1313,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -1324,7 +1701,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -1338,7 +1715,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -1349,7 +1726,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -1360,7 +1737,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -1371,7 +1748,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>39</v>
       </c>
@@ -1382,7 +1759,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>39</v>
       </c>
@@ -1393,7 +1770,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>39</v>
       </c>
@@ -1404,7 +1781,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -1415,7 +1792,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>39</v>
       </c>
@@ -1426,7 +1803,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -1437,7 +1814,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>39</v>
       </c>
@@ -1448,7 +1825,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>39</v>
       </c>
@@ -1459,7 +1836,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>39</v>
       </c>
@@ -1470,7 +1847,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>39</v>
       </c>
@@ -1481,7 +1858,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -1492,7 +1869,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>39</v>
       </c>
@@ -1503,7 +1880,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>39</v>
       </c>
@@ -1514,7 +1891,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>39</v>
       </c>
@@ -1525,7 +1902,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>40</v>
       </c>
@@ -1539,7 +1916,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>40</v>
       </c>
@@ -1550,7 +1927,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>40</v>
       </c>
@@ -1561,7 +1938,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>40</v>
       </c>
@@ -1572,7 +1949,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>40</v>
       </c>
@@ -1583,7 +1960,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>40</v>
       </c>
@@ -1594,7 +1971,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>40</v>
       </c>
@@ -1605,7 +1982,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>40</v>
       </c>
@@ -1616,7 +1993,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>40</v>
       </c>
@@ -1627,7 +2004,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>40</v>
       </c>
@@ -1638,7 +2015,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>40</v>
       </c>
@@ -1649,7 +2026,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>40</v>
       </c>
@@ -1660,7 +2037,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>40</v>
       </c>
@@ -1671,7 +2048,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>40</v>
       </c>
@@ -1682,7 +2059,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>40</v>
       </c>
@@ -1693,7 +2070,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>40</v>
       </c>
@@ -1704,7 +2081,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>40</v>
       </c>
@@ -1715,7 +2092,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>41</v>
       </c>
@@ -1729,7 +2106,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>41</v>
       </c>
@@ -1740,7 +2117,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>41</v>
       </c>
@@ -1751,7 +2128,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>41</v>
       </c>
@@ -1762,7 +2139,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>41</v>
       </c>
@@ -1773,7 +2150,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>41</v>
       </c>
@@ -1784,7 +2161,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>41</v>
       </c>
@@ -1795,7 +2172,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>41</v>
       </c>
@@ -1806,7 +2183,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>41</v>
       </c>
@@ -1817,7 +2194,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>41</v>
       </c>
@@ -1828,7 +2205,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>41</v>
       </c>
@@ -1839,7 +2216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>41</v>
       </c>
@@ -1850,7 +2227,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>41</v>
       </c>
@@ -1861,7 +2238,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>41</v>
       </c>
@@ -1872,7 +2249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>41</v>
       </c>
@@ -1883,7 +2260,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>41</v>
       </c>
@@ -1894,7 +2271,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>41</v>
       </c>
@@ -1905,7 +2282,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>41</v>
       </c>
@@ -1916,7 +2293,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>49</v>
       </c>
@@ -1930,7 +2307,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>49</v>
       </c>
@@ -1941,7 +2318,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>49</v>
       </c>
@@ -1952,7 +2329,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>49</v>
       </c>
@@ -1963,7 +2340,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>49</v>
       </c>
@@ -1974,7 +2351,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>49</v>
       </c>
@@ -1985,7 +2362,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>49</v>
       </c>
@@ -1996,7 +2373,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>49</v>
       </c>
@@ -2007,7 +2384,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>49</v>
       </c>
@@ -2018,7 +2395,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>49</v>
       </c>
@@ -2029,7 +2406,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>49</v>
       </c>
@@ -2040,7 +2417,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>49</v>
       </c>
@@ -2051,7 +2428,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>49</v>
       </c>
@@ -2062,7 +2439,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>49</v>
       </c>
@@ -2073,7 +2450,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>49</v>
       </c>
@@ -2084,7 +2461,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>49</v>
       </c>
@@ -2095,7 +2472,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>49</v>
       </c>
@@ -2106,7 +2483,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>49</v>
       </c>
@@ -2117,7 +2494,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>50</v>
       </c>
@@ -2131,7 +2508,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>50</v>
       </c>
@@ -2142,7 +2519,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>50</v>
       </c>
@@ -2153,7 +2530,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>50</v>
       </c>
@@ -2164,7 +2541,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>50</v>
       </c>
@@ -2175,7 +2552,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>50</v>
       </c>
@@ -2186,7 +2563,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>50</v>
       </c>
@@ -2197,7 +2574,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>50</v>
       </c>
@@ -2208,7 +2585,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>50</v>
       </c>
@@ -2219,7 +2596,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>50</v>
       </c>
@@ -2230,7 +2607,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>50</v>
       </c>
@@ -2241,7 +2618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>50</v>
       </c>
@@ -2252,7 +2629,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>50</v>
       </c>
@@ -2263,7 +2640,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>50</v>
       </c>
@@ -2274,7 +2651,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>50</v>
       </c>
@@ -2285,7 +2662,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>50</v>
       </c>
@@ -2296,7 +2673,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>50</v>
       </c>
@@ -2307,7 +2684,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>50</v>
       </c>
@@ -2327,14 +2704,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958711E3-6C4F-4BD5-AB6C-48EB3BBDFE40}">
   <dimension ref="A1:D220"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2348,7 +2725,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2362,7 +2739,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2373,7 +2750,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2384,7 +2761,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2395,7 +2772,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2406,7 +2783,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -2417,7 +2794,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -2428,7 +2805,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -2439,7 +2816,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -2450,7 +2827,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -2461,7 +2838,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -2472,7 +2849,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -2483,7 +2860,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -2494,7 +2871,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -2505,7 +2882,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -2516,7 +2893,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -2527,7 +2904,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -2538,7 +2915,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -2549,7 +2926,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -2560,7 +2937,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -2571,7 +2948,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -2582,7 +2959,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -2593,7 +2970,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -2604,7 +2981,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -2615,7 +2992,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -2626,7 +3003,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -2637,7 +3014,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -2648,7 +3025,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -2659,7 +3036,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -2670,7 +3047,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -2681,7 +3058,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -2695,7 +3072,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>27</v>
       </c>
@@ -2706,7 +3083,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -2717,7 +3094,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -2728,7 +3105,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -2739,7 +3116,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -2750,7 +3127,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -2761,7 +3138,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -2772,7 +3149,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -2783,7 +3160,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -2794,7 +3171,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -2805,7 +3182,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -2816,7 +3193,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>27</v>
       </c>
@@ -2827,7 +3204,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>27</v>
       </c>
@@ -2838,7 +3215,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -2849,7 +3226,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>27</v>
       </c>
@@ -2860,7 +3237,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>27</v>
       </c>
@@ -2871,7 +3248,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>27</v>
       </c>
@@ -2882,7 +3259,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>27</v>
       </c>
@@ -2893,7 +3270,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>27</v>
       </c>
@@ -2904,7 +3281,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>27</v>
       </c>
@@ -2915,7 +3292,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>27</v>
       </c>
@@ -2926,7 +3303,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>27</v>
       </c>
@@ -2937,7 +3314,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>27</v>
       </c>
@@ -2948,7 +3325,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>27</v>
       </c>
@@ -2959,7 +3336,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>27</v>
       </c>
@@ -2970,7 +3347,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>27</v>
       </c>
@@ -2981,7 +3358,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>27</v>
       </c>
@@ -2992,7 +3369,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>27</v>
       </c>
@@ -3003,7 +3380,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -3017,7 +3394,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>39</v>
       </c>
@@ -3028,7 +3405,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>39</v>
       </c>
@@ -3039,7 +3416,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>39</v>
       </c>
@@ -3050,7 +3427,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>39</v>
       </c>
@@ -3061,7 +3438,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>39</v>
       </c>
@@ -3072,7 +3449,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>39</v>
       </c>
@@ -3083,7 +3460,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>39</v>
       </c>
@@ -3094,7 +3471,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>39</v>
       </c>
@@ -3105,7 +3482,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>39</v>
       </c>
@@ -3116,7 +3493,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>39</v>
       </c>
@@ -3127,7 +3504,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>39</v>
       </c>
@@ -3138,7 +3515,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>39</v>
       </c>
@@ -3149,7 +3526,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>39</v>
       </c>
@@ -3160,7 +3537,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>39</v>
       </c>
@@ -3171,7 +3548,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>39</v>
       </c>
@@ -3182,7 +3559,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>39</v>
       </c>
@@ -3193,7 +3570,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>39</v>
       </c>
@@ -3204,7 +3581,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>39</v>
       </c>
@@ -3215,7 +3592,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>39</v>
       </c>
@@ -3226,7 +3603,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>39</v>
       </c>
@@ -3237,7 +3614,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>39</v>
       </c>
@@ -3248,7 +3625,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>39</v>
       </c>
@@ -3259,7 +3636,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>39</v>
       </c>
@@ -3270,7 +3647,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>39</v>
       </c>
@@ -3281,7 +3658,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>39</v>
       </c>
@@ -3292,7 +3669,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>39</v>
       </c>
@@ -3303,7 +3680,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>39</v>
       </c>
@@ -3314,7 +3691,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>39</v>
       </c>
@@ -3325,7 +3702,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>39</v>
       </c>
@@ -3336,7 +3713,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>40</v>
       </c>
@@ -3350,7 +3727,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>40</v>
       </c>
@@ -3361,7 +3738,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>40</v>
       </c>
@@ -3372,7 +3749,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -3383,7 +3760,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>40</v>
       </c>
@@ -3394,7 +3771,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -3405,7 +3782,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>40</v>
       </c>
@@ -3416,7 +3793,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -3427,7 +3804,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -3438,7 +3815,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -3449,7 +3826,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>40</v>
       </c>
@@ -3460,7 +3837,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>40</v>
       </c>
@@ -3471,7 +3848,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -3482,7 +3859,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>40</v>
       </c>
@@ -3493,7 +3870,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>40</v>
       </c>
@@ -3504,7 +3881,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>40</v>
       </c>
@@ -3515,7 +3892,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>40</v>
       </c>
@@ -3526,7 +3903,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>40</v>
       </c>
@@ -3537,7 +3914,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -3548,7 +3925,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>40</v>
       </c>
@@ -3559,7 +3936,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>40</v>
       </c>
@@ -3570,7 +3947,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>40</v>
       </c>
@@ -3581,7 +3958,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>40</v>
       </c>
@@ -3592,7 +3969,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>40</v>
       </c>
@@ -3603,7 +3980,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>40</v>
       </c>
@@ -3614,7 +3991,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>40</v>
       </c>
@@ -3625,7 +4002,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>40</v>
       </c>
@@ -3636,7 +4013,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>40</v>
       </c>
@@ -3647,7 +4024,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>40</v>
       </c>
@@ -3658,7 +4035,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>40</v>
       </c>
@@ -3669,7 +4046,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>40</v>
       </c>
@@ -3680,7 +4057,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>40</v>
       </c>
@@ -3691,7 +4068,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>40</v>
       </c>
@@ -3702,7 +4079,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>40</v>
       </c>
@@ -3713,7 +4090,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>41</v>
       </c>
@@ -3727,7 +4104,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>41</v>
       </c>
@@ -3738,7 +4115,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>41</v>
       </c>
@@ -3749,7 +4126,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>41</v>
       </c>
@@ -3760,7 +4137,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>41</v>
       </c>
@@ -3771,7 +4148,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>41</v>
       </c>
@@ -3782,7 +4159,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>41</v>
       </c>
@@ -3793,7 +4170,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>41</v>
       </c>
@@ -3804,7 +4181,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>41</v>
       </c>
@@ -3815,7 +4192,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>41</v>
       </c>
@@ -3826,7 +4203,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>41</v>
       </c>
@@ -3837,7 +4214,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>41</v>
       </c>
@@ -3848,7 +4225,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>41</v>
       </c>
@@ -3859,7 +4236,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>41</v>
       </c>
@@ -3870,7 +4247,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>41</v>
       </c>
@@ -3881,7 +4258,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>41</v>
       </c>
@@ -3892,7 +4269,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>41</v>
       </c>
@@ -3903,7 +4280,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>41</v>
       </c>
@@ -3914,7 +4291,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>41</v>
       </c>
@@ -3925,7 +4302,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>41</v>
       </c>
@@ -3936,7 +4313,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>41</v>
       </c>
@@ -3947,7 +4324,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>41</v>
       </c>
@@ -3958,7 +4335,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>41</v>
       </c>
@@ -3969,7 +4346,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>41</v>
       </c>
@@ -3980,7 +4357,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>41</v>
       </c>
@@ -3991,7 +4368,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>41</v>
       </c>
@@ -4002,7 +4379,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>41</v>
       </c>
@@ -4013,7 +4390,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>41</v>
       </c>
@@ -4024,7 +4401,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>41</v>
       </c>
@@ -4035,7 +4412,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>41</v>
       </c>
@@ -4046,7 +4423,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>49</v>
       </c>
@@ -4060,7 +4437,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>49</v>
       </c>
@@ -4071,7 +4448,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>49</v>
       </c>
@@ -4082,7 +4459,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>49</v>
       </c>
@@ -4093,7 +4470,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>49</v>
       </c>
@@ -4104,7 +4481,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>49</v>
       </c>
@@ -4115,7 +4492,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>49</v>
       </c>
@@ -4126,7 +4503,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>49</v>
       </c>
@@ -4137,7 +4514,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>49</v>
       </c>
@@ -4148,7 +4525,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>49</v>
       </c>
@@ -4159,7 +4536,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>49</v>
       </c>
@@ -4170,7 +4547,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>49</v>
       </c>
@@ -4181,7 +4558,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>49</v>
       </c>
@@ -4192,7 +4569,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>49</v>
       </c>
@@ -4203,7 +4580,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>49</v>
       </c>
@@ -4214,7 +4591,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>49</v>
       </c>
@@ -4225,7 +4602,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>49</v>
       </c>
@@ -4236,7 +4613,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>49</v>
       </c>
@@ -4247,7 +4624,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>49</v>
       </c>
@@ -4258,7 +4635,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>49</v>
       </c>
@@ -4269,7 +4646,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>49</v>
       </c>
@@ -4280,7 +4657,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>49</v>
       </c>
@@ -4291,7 +4668,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>49</v>
       </c>
@@ -4302,7 +4679,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>49</v>
       </c>
@@ -4313,7 +4690,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>49</v>
       </c>
@@ -4324,7 +4701,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>49</v>
       </c>
@@ -4335,7 +4712,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>49</v>
       </c>
@@ -4346,7 +4723,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>49</v>
       </c>
@@ -4357,7 +4734,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>49</v>
       </c>
@@ -4368,7 +4745,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>50</v>
       </c>
@@ -4382,7 +4759,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>50</v>
       </c>
@@ -4393,7 +4770,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>50</v>
       </c>
@@ -4404,7 +4781,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>50</v>
       </c>
@@ -4415,7 +4792,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>50</v>
       </c>
@@ -4426,7 +4803,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>50</v>
       </c>
@@ -4437,7 +4814,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>50</v>
       </c>
@@ -4448,7 +4825,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>50</v>
       </c>
@@ -4459,7 +4836,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>50</v>
       </c>
@@ -4470,7 +4847,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>50</v>
       </c>
@@ -4481,7 +4858,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>50</v>
       </c>
@@ -4492,7 +4869,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>50</v>
       </c>
@@ -4503,7 +4880,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>50</v>
       </c>
@@ -4514,7 +4891,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>50</v>
       </c>
@@ -4525,7 +4902,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>50</v>
       </c>
@@ -4536,7 +4913,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>50</v>
       </c>
@@ -4547,7 +4924,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>50</v>
       </c>
@@ -4558,7 +4935,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>50</v>
       </c>
@@ -4569,7 +4946,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>50</v>
       </c>
@@ -4580,7 +4957,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>50</v>
       </c>
@@ -4591,7 +4968,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>50</v>
       </c>
@@ -4602,7 +4979,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>50</v>
       </c>
@@ -4613,7 +4990,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>50</v>
       </c>
@@ -4624,7 +5001,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>50</v>
       </c>
@@ -4635,7 +5012,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>50</v>
       </c>
@@ -4646,7 +5023,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>50</v>
       </c>
@@ -4657,7 +5034,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>50</v>
       </c>
@@ -4668,7 +5045,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>50</v>
       </c>
@@ -4679,7 +5056,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>50</v>
       </c>
@@ -4690,7 +5067,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>50</v>
       </c>
@@ -4710,9 +5087,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17D1D00-0203-4AF7-89F9-FDB785A93226}">
   <dimension ref="A1:D220"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4726,7 +5103,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -4740,7 +5117,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -4751,7 +5128,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4762,7 +5139,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4773,7 +5150,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -4784,7 +5161,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -4795,7 +5172,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -4806,7 +5183,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -4817,7 +5194,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -4828,7 +5205,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -4839,7 +5216,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -4850,7 +5227,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -4861,7 +5238,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -4872,7 +5249,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -4883,7 +5260,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -4894,7 +5271,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -4905,7 +5282,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -4916,7 +5293,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -4927,7 +5304,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -4938,7 +5315,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -4949,7 +5326,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -4960,7 +5337,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -4971,7 +5348,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -4982,7 +5359,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -4993,7 +5370,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -5004,7 +5381,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -5015,7 +5392,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -5026,7 +5403,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -5037,7 +5414,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -5048,7 +5425,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -5059,7 +5436,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -5073,7 +5450,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>27</v>
       </c>
@@ -5084,7 +5461,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -5095,7 +5472,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -5106,7 +5483,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -5117,7 +5494,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -5128,7 +5505,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -5139,7 +5516,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -5150,7 +5527,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -5161,7 +5538,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -5172,7 +5549,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -5183,7 +5560,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -5194,7 +5571,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>27</v>
       </c>
@@ -5205,7 +5582,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>27</v>
       </c>
@@ -5216,7 +5593,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -5227,7 +5604,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>27</v>
       </c>
@@ -5238,7 +5615,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>27</v>
       </c>
@@ -5249,7 +5626,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>27</v>
       </c>
@@ -5260,7 +5637,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>27</v>
       </c>
@@ -5271,7 +5648,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>27</v>
       </c>
@@ -5282,7 +5659,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>27</v>
       </c>
@@ -5293,7 +5670,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>27</v>
       </c>
@@ -5304,7 +5681,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>27</v>
       </c>
@@ -5315,7 +5692,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>27</v>
       </c>
@@ -5326,7 +5703,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>27</v>
       </c>
@@ -5337,7 +5714,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>27</v>
       </c>
@@ -5348,7 +5725,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>27</v>
       </c>
@@ -5359,7 +5736,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>27</v>
       </c>
@@ -5370,7 +5747,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>27</v>
       </c>
@@ -5381,7 +5758,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -5395,7 +5772,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>39</v>
       </c>
@@ -5406,7 +5783,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>39</v>
       </c>
@@ -5417,7 +5794,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>39</v>
       </c>
@@ -5428,7 +5805,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>39</v>
       </c>
@@ -5439,7 +5816,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>39</v>
       </c>
@@ -5450,7 +5827,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>39</v>
       </c>
@@ -5461,7 +5838,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>39</v>
       </c>
@@ -5472,7 +5849,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>39</v>
       </c>
@@ -5483,7 +5860,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>39</v>
       </c>
@@ -5494,7 +5871,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>39</v>
       </c>
@@ -5505,7 +5882,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>39</v>
       </c>
@@ -5516,7 +5893,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>39</v>
       </c>
@@ -5527,7 +5904,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>39</v>
       </c>
@@ -5538,7 +5915,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>39</v>
       </c>
@@ -5549,7 +5926,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>39</v>
       </c>
@@ -5560,7 +5937,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>39</v>
       </c>
@@ -5571,7 +5948,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>39</v>
       </c>
@@ -5582,7 +5959,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>39</v>
       </c>
@@ -5593,7 +5970,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>39</v>
       </c>
@@ -5604,7 +5981,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>39</v>
       </c>
@@ -5615,7 +5992,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>39</v>
       </c>
@@ -5626,7 +6003,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>39</v>
       </c>
@@ -5637,7 +6014,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>39</v>
       </c>
@@ -5648,7 +6025,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>39</v>
       </c>
@@ -5659,7 +6036,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>39</v>
       </c>
@@ -5670,7 +6047,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>39</v>
       </c>
@@ -5681,7 +6058,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>39</v>
       </c>
@@ -5692,7 +6069,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>39</v>
       </c>
@@ -5703,7 +6080,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>39</v>
       </c>
@@ -5714,7 +6091,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>40</v>
       </c>
@@ -5728,7 +6105,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>40</v>
       </c>
@@ -5739,7 +6116,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>40</v>
       </c>
@@ -5750,7 +6127,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -5761,7 +6138,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>40</v>
       </c>
@@ -5772,7 +6149,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -5783,7 +6160,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>40</v>
       </c>
@@ -5794,7 +6171,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -5805,7 +6182,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -5816,7 +6193,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -5827,7 +6204,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>40</v>
       </c>
@@ -5838,7 +6215,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>40</v>
       </c>
@@ -5849,7 +6226,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -5860,7 +6237,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>40</v>
       </c>
@@ -5871,7 +6248,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>40</v>
       </c>
@@ -5882,7 +6259,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>40</v>
       </c>
@@ -5893,7 +6270,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>40</v>
       </c>
@@ -5904,7 +6281,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>40</v>
       </c>
@@ -5915,7 +6292,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -5926,7 +6303,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>40</v>
       </c>
@@ -5937,7 +6314,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>40</v>
       </c>
@@ -5948,7 +6325,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>40</v>
       </c>
@@ -5959,7 +6336,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>40</v>
       </c>
@@ -5970,7 +6347,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>40</v>
       </c>
@@ -5981,7 +6358,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>40</v>
       </c>
@@ -5992,7 +6369,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>40</v>
       </c>
@@ -6003,7 +6380,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>40</v>
       </c>
@@ -6014,7 +6391,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>40</v>
       </c>
@@ -6025,7 +6402,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>40</v>
       </c>
@@ -6036,7 +6413,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>40</v>
       </c>
@@ -6047,7 +6424,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>40</v>
       </c>
@@ -6058,7 +6435,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>40</v>
       </c>
@@ -6069,7 +6446,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>40</v>
       </c>
@@ -6080,7 +6457,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>40</v>
       </c>
@@ -6091,7 +6468,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>41</v>
       </c>
@@ -6105,7 +6482,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>41</v>
       </c>
@@ -6116,7 +6493,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>41</v>
       </c>
@@ -6127,7 +6504,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>41</v>
       </c>
@@ -6138,7 +6515,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>41</v>
       </c>
@@ -6149,7 +6526,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>41</v>
       </c>
@@ -6160,7 +6537,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>41</v>
       </c>
@@ -6171,7 +6548,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>41</v>
       </c>
@@ -6182,7 +6559,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>41</v>
       </c>
@@ -6193,7 +6570,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>41</v>
       </c>
@@ -6204,7 +6581,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>41</v>
       </c>
@@ -6215,7 +6592,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>41</v>
       </c>
@@ -6226,7 +6603,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>41</v>
       </c>
@@ -6237,7 +6614,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>41</v>
       </c>
@@ -6248,7 +6625,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>41</v>
       </c>
@@ -6259,7 +6636,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>41</v>
       </c>
@@ -6270,7 +6647,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>41</v>
       </c>
@@ -6281,7 +6658,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>41</v>
       </c>
@@ -6292,7 +6669,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>41</v>
       </c>
@@ -6303,7 +6680,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>41</v>
       </c>
@@ -6314,7 +6691,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>41</v>
       </c>
@@ -6325,7 +6702,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>41</v>
       </c>
@@ -6336,7 +6713,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>41</v>
       </c>
@@ -6347,7 +6724,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>41</v>
       </c>
@@ -6358,7 +6735,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>41</v>
       </c>
@@ -6369,7 +6746,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>41</v>
       </c>
@@ -6380,7 +6757,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>41</v>
       </c>
@@ -6391,7 +6768,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>41</v>
       </c>
@@ -6402,7 +6779,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>41</v>
       </c>
@@ -6413,7 +6790,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>41</v>
       </c>
@@ -6424,7 +6801,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>49</v>
       </c>
@@ -6438,7 +6815,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>49</v>
       </c>
@@ -6449,7 +6826,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>49</v>
       </c>
@@ -6460,7 +6837,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>49</v>
       </c>
@@ -6471,7 +6848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>49</v>
       </c>
@@ -6482,7 +6859,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>49</v>
       </c>
@@ -6493,7 +6870,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>49</v>
       </c>
@@ -6504,7 +6881,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>49</v>
       </c>
@@ -6515,7 +6892,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>49</v>
       </c>
@@ -6526,7 +6903,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>49</v>
       </c>
@@ -6537,7 +6914,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>49</v>
       </c>
@@ -6548,7 +6925,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>49</v>
       </c>
@@ -6559,7 +6936,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>49</v>
       </c>
@@ -6570,7 +6947,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>49</v>
       </c>
@@ -6581,7 +6958,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>49</v>
       </c>
@@ -6592,7 +6969,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>49</v>
       </c>
@@ -6603,7 +6980,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>49</v>
       </c>
@@ -6614,7 +6991,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>49</v>
       </c>
@@ -6625,7 +7002,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>49</v>
       </c>
@@ -6636,7 +7013,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>49</v>
       </c>
@@ -6647,7 +7024,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>49</v>
       </c>
@@ -6658,7 +7035,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>49</v>
       </c>
@@ -6669,7 +7046,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>49</v>
       </c>
@@ -6680,7 +7057,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>49</v>
       </c>
@@ -6691,7 +7068,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>49</v>
       </c>
@@ -6702,7 +7079,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>49</v>
       </c>
@@ -6713,7 +7090,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>49</v>
       </c>
@@ -6724,7 +7101,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>49</v>
       </c>
@@ -6735,7 +7112,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>49</v>
       </c>
@@ -6746,7 +7123,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>50</v>
       </c>
@@ -6760,7 +7137,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>50</v>
       </c>
@@ -6771,7 +7148,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>50</v>
       </c>
@@ -6782,7 +7159,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>50</v>
       </c>
@@ -6793,7 +7170,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>50</v>
       </c>
@@ -6804,7 +7181,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>50</v>
       </c>
@@ -6815,7 +7192,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>50</v>
       </c>
@@ -6826,7 +7203,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>50</v>
       </c>
@@ -6837,7 +7214,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>50</v>
       </c>
@@ -6848,7 +7225,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>50</v>
       </c>
@@ -6859,7 +7236,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>50</v>
       </c>
@@ -6870,7 +7247,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>50</v>
       </c>
@@ -6881,7 +7258,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>50</v>
       </c>
@@ -6892,7 +7269,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>50</v>
       </c>
@@ -6903,7 +7280,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>50</v>
       </c>
@@ -6914,7 +7291,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>50</v>
       </c>
@@ -6925,7 +7302,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>50</v>
       </c>
@@ -6936,7 +7313,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>50</v>
       </c>
@@ -6947,7 +7324,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>50</v>
       </c>
@@ -6958,7 +7335,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>50</v>
       </c>
@@ -6969,7 +7346,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>50</v>
       </c>
@@ -6980,7 +7357,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>50</v>
       </c>
@@ -6991,7 +7368,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>50</v>
       </c>
@@ -7002,7 +7379,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>50</v>
       </c>
@@ -7013,7 +7390,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>50</v>
       </c>
@@ -7024,7 +7401,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>50</v>
       </c>
@@ -7035,7 +7412,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>50</v>
       </c>
@@ -7046,7 +7423,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>50</v>
       </c>
@@ -7057,7 +7434,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>50</v>
       </c>
@@ -7068,7 +7445,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>50</v>
       </c>
@@ -7087,14 +7464,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96E5C589-12B6-46D0-ACA0-F15124B14248}">
   <dimension ref="A1:D49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5546875" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7108,263 +7485,263 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
         <v>124</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" t="s">
-        <v>181</v>
-      </c>
       <c r="C3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>49</v>
       </c>
       <c r="B12" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>49</v>
       </c>
       <c r="B13" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C15" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C17" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C18" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C19" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C20" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C22" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="C24" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -7375,7 +7752,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -7386,7 +7763,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -7394,10 +7771,10 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>49</v>
       </c>
@@ -7405,10 +7782,10 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>49</v>
       </c>
@@ -7416,10 +7793,10 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -7427,10 +7804,10 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -7438,10 +7815,10 @@
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -7449,10 +7826,10 @@
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>49</v>
       </c>
@@ -7460,10 +7837,10 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>49</v>
       </c>
@@ -7471,10 +7848,10 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -7482,10 +7859,10 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -7493,10 +7870,10 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>49</v>
       </c>
@@ -7504,10 +7881,10 @@
         <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>49</v>
       </c>
@@ -7515,10 +7892,10 @@
         <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>49</v>
       </c>
@@ -7526,10 +7903,10 @@
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>49</v>
       </c>
@@ -7540,7 +7917,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -7548,10 +7925,10 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -7559,10 +7936,10 @@
         <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>49</v>
       </c>
@@ -7570,10 +7947,10 @@
         <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -7581,10 +7958,10 @@
         <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -7595,7 +7972,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -7603,10 +7980,10 @@
         <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -7614,10 +7991,10 @@
         <v>10</v>
       </c>
       <c r="C47" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -7625,10 +8002,10 @@
         <v>10</v>
       </c>
       <c r="C48" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -7636,7 +8013,7 @@
         <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -7647,14 +8024,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64ED07A9-2F73-4233-8727-B6937003F0D4}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D92"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7668,80 +8047,2018 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>49</v>
       </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
       <c r="C3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
       <c r="C4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
       <c r="C5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>124</v>
+      </c>
       <c r="C6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
       <c r="C7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>124</v>
+      </c>
       <c r="C8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>124</v>
+      </c>
       <c r="C9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>124</v>
+      </c>
       <c r="C10" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>124</v>
+      </c>
       <c r="C11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
       <c r="C12" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
       <c r="C13" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
       <c r="C14" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s">
+        <v>124</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" t="s">
+        <v>124</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" t="s">
+        <v>124</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" t="s">
+        <v>124</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" t="s">
+        <v>124</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" t="s">
+        <v>124</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B56" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B57" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B59" t="s">
+        <v>124</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B60" t="s">
+        <v>124</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B61" t="s">
+        <v>124</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B62" t="s">
+        <v>124</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B63" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s">
+        <v>5</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B71" t="s">
+        <v>124</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72" t="s">
+        <v>124</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B73" t="s">
+        <v>124</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" t="s">
+        <v>124</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B75" t="s">
+        <v>124</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" t="s">
+        <v>124</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B79" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B80" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B81" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B82" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B83" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B84" t="s">
+        <v>124</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B85" t="s">
+        <v>124</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B86" t="s">
+        <v>124</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B87" t="s">
+        <v>124</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B88" t="s">
+        <v>124</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B89" t="s">
+        <v>124</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B90" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B91" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B92" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C92B042-D4FF-2640-8B1F-B7EB4E9D16D9}">
+  <dimension ref="A1:D189"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C5" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C7" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C9" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C10" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C11" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C12" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C13" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C14" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C15" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C16" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C22" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C24" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C26" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C28" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C29" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C30" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C31" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C32" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C35" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C36" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C37" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C38" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C39" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C40" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C41" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C42" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="43" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C43" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C44" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="45" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C45" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="46" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C46" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="47" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C47" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C48" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C49" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C50" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C52" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C53" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="C54" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C55" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C56" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C57" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C58" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C59" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C60" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C61" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C62" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C63" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C64" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C65" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C66" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C67" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C68" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C69" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C70" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C71" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C72" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C73" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C74" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C75" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C76" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C77" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C78" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C80" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C81" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C82" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C83" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C84" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C85" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C86" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C87" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C88" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C89" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C90" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C91" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C92" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C93" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C94" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C95" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C96" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C97" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C98" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C99" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C100" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C101" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C102" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C103" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C104" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C105" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C106" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C108" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C109" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C110" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C111" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C112" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C113" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C114" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C115" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C116" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C117" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C118" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C119" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C120" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C121" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="122" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C122" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="123" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C123" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="124" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C124" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="125" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C125" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="126" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C126" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="127" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C127" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C128" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C129" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C130" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C131" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C132" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C133" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C134" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C136" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C137" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C138" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C139" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C140" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C141" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C142" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C143" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C144" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="145" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C145" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="146" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C146" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="147" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C147" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="148" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C148" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="149" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C149" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="150" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C150" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="151" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C151" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="152" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C152" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="153" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C153" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="154" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C154" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="155" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C155" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C156" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="157" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C157" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="158" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C158" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="159" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C159" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="160" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C160" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C161" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C162" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C164" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C165" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C166" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C167" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C168" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C169" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C170" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C171" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C172" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C173" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C174" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C175" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C176" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="177" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C177" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="178" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C178" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="179" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C179" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="180" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C180" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="181" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C181" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="182" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C182" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C183" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="184" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C184" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="185" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C185" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="186" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C186" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="187" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C187" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="188" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C188" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="189" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C189" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/restaurant_menus.xlsx
+++ b/restaurant_menus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ooredoomle-my.sharepoint.com/personal/ahmed_maail_ooredoo_mv/Documents/vishaal idea/ramadan menu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="466" documentId="11_F25DC773A252ABDACC1048D4395F6C085BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AC237CA-34C0-41AA-91C3-DF74B507E2A3}"/>
+  <xr:revisionPtr revIDLastSave="656" documentId="11_F25DC773A252ABDACC1048D4395F6C085BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D2E78DA-3F94-4CF1-B02E-40F0315D2A15}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mamak" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="pomelo" sheetId="3" r:id="rId3"/>
     <sheet name="buruzu" sheetId="4" r:id="rId4"/>
     <sheet name="house of flavors" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
+    <sheet name="Acha's Poppadums" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2300" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2514" uniqueCount="271">
   <si>
     <t>Day</t>
   </si>
@@ -673,284 +674,194 @@
     <t>Aloo Gobi</t>
   </si>
   <si>
-    <t>Karaafani</t>
-  </si>
-  <si>
-    <t>Caesar Salad</t>
-  </si>
-  <si>
-    <t>Greek Salad</t>
-  </si>
-  <si>
-    <t>Roshi &amp; Battura</t>
-  </si>
-  <si>
-    <t>Mongolian Fried Rice</t>
-  </si>
-  <si>
-    <t>Penne Alfredo</t>
-  </si>
-  <si>
-    <t>Mustard Honey Chicken</t>
-  </si>
-  <si>
-    <t>Kan Kun Beef</t>
-  </si>
-  <si>
-    <t>Kulhi Mas</t>
-  </si>
-  <si>
-    <t>Aalu Gobi</t>
-  </si>
-  <si>
-    <t>Vegetable Chopsuey</t>
-  </si>
-  <si>
-    <t>Omaali</t>
-  </si>
-  <si>
-    <t>Blueberry Cheesecake</t>
-  </si>
-  <si>
-    <t>Assorted Fresh Fruits</t>
-  </si>
-  <si>
-    <t>Tea or Coffee</t>
-  </si>
-  <si>
-    <t>Water &amp; Nuts</t>
-  </si>
-  <si>
-    <t>Passionfruit Juice</t>
+    <t>FRIDAY</t>
+  </si>
+  <si>
+    <t>Drinks</t>
+  </si>
+  <si>
+    <t>Water melon</t>
+  </si>
+  <si>
+    <t>MVR 175+ GST</t>
+  </si>
+  <si>
+    <t>Mixed Fruit</t>
+  </si>
+  <si>
+    <t>Main Course</t>
+  </si>
+  <si>
+    <t>Schezwan Chicken</t>
+  </si>
+  <si>
+    <t>Beef Masala</t>
+  </si>
+  <si>
+    <t>Aalo Mutter</t>
+  </si>
+  <si>
+    <t>Tuna Noodles</t>
+  </si>
+  <si>
+    <t>Breads</t>
+  </si>
+  <si>
+    <t>Butter Naan</t>
+  </si>
+  <si>
+    <t>Paratta</t>
+  </si>
+  <si>
+    <t>Salad</t>
+  </si>
+  <si>
+    <t>Mixed Salad</t>
+  </si>
+  <si>
+    <t>Cut Fruits</t>
+  </si>
+  <si>
+    <t>Betel nuts</t>
+  </si>
+  <si>
+    <t>Tea/Coffee</t>
+  </si>
+  <si>
+    <t>Dessert</t>
+  </si>
+  <si>
+    <t>Rice Kheer</t>
+  </si>
+  <si>
+    <t>Gulab jamun</t>
+  </si>
+  <si>
+    <t>MONDAY</t>
+  </si>
+  <si>
+    <t>Pineapple</t>
+  </si>
+  <si>
+    <t>Chicken Fried Rice</t>
+  </si>
+  <si>
+    <t>Chicken Tikka Masala</t>
+  </si>
+  <si>
+    <t>Fish Manchurian</t>
+  </si>
+  <si>
+    <t>Mushroom &amp; Green peas</t>
+  </si>
+  <si>
+    <t>Masala</t>
+  </si>
+  <si>
+    <t>Beef Noodles</t>
+  </si>
+  <si>
+    <t>Roshi, Chapathi</t>
+  </si>
+  <si>
+    <t>Indian Garden Salad</t>
+  </si>
+  <si>
+    <t>Beetle nuts</t>
+  </si>
+  <si>
+    <t>Carrot Halwa</t>
+  </si>
+  <si>
+    <t>SATURDAY</t>
+  </si>
+  <si>
+    <t>Egg Noodles</t>
+  </si>
+  <si>
+    <t>Butter Chicken</t>
+  </si>
+  <si>
+    <t>Devilled Fish</t>
+  </si>
+  <si>
+    <t>Schezwan Chicken Rice</t>
+  </si>
+  <si>
+    <t>SUNDAY</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>Beef Rogan josh</t>
+  </si>
+  <si>
+    <t>Aaloo Gobi Masala</t>
   </si>
   <si>
     <t>Green Salad</t>
   </si>
   <si>
-    <t>Roshi &amp; Fen Folhi</t>
-  </si>
-  <si>
-    <t>Macaroni Carbonara</t>
-  </si>
-  <si>
-    <t>Tandoori Chicken</t>
-  </si>
-  <si>
-    <t>Beef Bulgogi</t>
-  </si>
-  <si>
-    <t>Kandu Kukulhu</t>
-  </si>
-  <si>
-    <t>Sri Lankan Devilled Potato</t>
-  </si>
-  <si>
-    <t>Vegetable Manchurian</t>
-  </si>
-  <si>
-    <t>***************</t>
-  </si>
-  <si>
-    <t>Passion Fruit Mousse</t>
-  </si>
-  <si>
-    <t>Tiramisu Cake</t>
-  </si>
-  <si>
-    <t>Sweet Filling</t>
-  </si>
-  <si>
-    <t>Refreshments</t>
-  </si>
-  <si>
-    <t>大大火大大大大大大文大大大大大</t>
-  </si>
-  <si>
-    <t>Salads</t>
-  </si>
-  <si>
-    <t>Bashi Mas Huni</t>
-  </si>
-  <si>
-    <t>Chinese Fried Rice</t>
-  </si>
-  <si>
-    <t>Spaghetti Melanzane</t>
-  </si>
-  <si>
-    <t>Boot Stoganirt</t>
-  </si>
-  <si>
-    <t>Lebanese Grilled Chicken</t>
-  </si>
-  <si>
-    <t>HanaaKuri Mas</t>
-  </si>
-  <si>
-    <t>Tempered Potato</t>
-  </si>
-  <si>
-    <t>Cinnamon Cake with Ganache</t>
-  </si>
-  <si>
-    <t>Fruit Gateaux</t>
-  </si>
-  <si>
-    <t>Cheese Cake</t>
-  </si>
-  <si>
-    <t>*火大大大火大大大火大火大大大</t>
-  </si>
-  <si>
-    <t>Mango Juice</t>
-  </si>
-  <si>
-    <t>Thai Beef Salad</t>
-  </si>
-  <si>
-    <t>Roshi &amp; Fenfolhi</t>
-  </si>
-  <si>
-    <t>Spinach Fried Rice</t>
-  </si>
-  <si>
-    <t>Penne Alla Rustica</t>
-  </si>
-  <si>
-    <t>Chicken Tikka Masala</t>
-  </si>
-  <si>
-    <t>Lebanese Beef Kebab</t>
-  </si>
-  <si>
-    <t>Hanaakuri Mas</t>
-  </si>
-  <si>
-    <t>Hungarian Potato</t>
-  </si>
-  <si>
-    <t>Sauteed Vegetables</t>
-  </si>
-  <si>
-    <t>"******t"**</t>
-  </si>
-  <si>
-    <t>Le Lait Gateau</t>
-  </si>
-  <si>
-    <t>Cheese Cakae</t>
-  </si>
-  <si>
-    <t>Guava Juice</t>
-  </si>
-  <si>
-    <t>*************★*</t>
-  </si>
-  <si>
-    <t>American Salad</t>
-  </si>
-  <si>
-    <t>Maldivian Tuna Salad</t>
-  </si>
-  <si>
-    <t>Roshi &amp; Paratta</t>
-  </si>
-  <si>
-    <t>Manchurian Fried Rice</t>
-  </si>
-  <si>
-    <t>Spaghetti Bolognese</t>
-  </si>
-  <si>
-    <t>Alfaham Chicken</t>
-  </si>
-  <si>
-    <t>Srilankan Beef Curry</t>
-  </si>
-  <si>
-    <t>Grilled Fish Lemon Butter</t>
-  </si>
-  <si>
-    <t>Vegetable Au Gratin</t>
-  </si>
-  <si>
-    <t>**************</t>
-  </si>
-  <si>
-    <t>Kiwi Gateaux</t>
-  </si>
-  <si>
-    <t>Sweet Fling</t>
-  </si>
-  <si>
-    <t>Karaafani®</t>
-  </si>
-  <si>
-    <t>Thai Chicken Salad</t>
-  </si>
-  <si>
-    <t>Roshi &amp; Yeast Roshi</t>
-  </si>
-  <si>
-    <t>Sweet Corn &amp; Sultan Rice</t>
-  </si>
-  <si>
-    <t>Penne Alla Salsa Rosa</t>
-  </si>
-  <si>
-    <t>Tandoori Shish Kebab</t>
-  </si>
-  <si>
-    <t>Mongolian Beef</t>
-  </si>
-  <si>
-    <t>Musamma Curry</t>
-  </si>
-  <si>
-    <t>Aubergine Provencal</t>
-  </si>
-  <si>
-    <t>***%**********</t>
-  </si>
-  <si>
-    <t>Chocolate Mousse</t>
-  </si>
-  <si>
-    <t>Kesari</t>
-  </si>
-  <si>
-    <t>New York Cheesecake</t>
-  </si>
-  <si>
-    <t>****★**********</t>
-  </si>
-  <si>
-    <t>Florist Green Salad</t>
-  </si>
-  <si>
-    <t>Mixed Vegetable Pulao</t>
-  </si>
-  <si>
-    <t>Spaghetti Aglio Olio</t>
-  </si>
-  <si>
-    <t>Lebanese Chicken</t>
-  </si>
-  <si>
-    <t>Deviled Fish</t>
-  </si>
-  <si>
-    <t>**********w</t>
-  </si>
-  <si>
-    <t>Cinnamon Chocolate</t>
+    <t>Shahi Tukda</t>
+  </si>
+  <si>
+    <t>TUESDAY</t>
+  </si>
+  <si>
+    <t>Pappaya</t>
+  </si>
+  <si>
+    <t>Chicken Dopiyaza</t>
+  </si>
+  <si>
+    <t>Devilled Beef</t>
+  </si>
+  <si>
+    <t>Sweet n Sour Fish</t>
+  </si>
+  <si>
+    <t>Gobi Manchurian</t>
+  </si>
+  <si>
+    <t>Garlic Naan</t>
+  </si>
+  <si>
+    <t>Mixed Veg Salad</t>
+  </si>
+  <si>
+    <t>Semiya Kheer</t>
+  </si>
+  <si>
+    <t>WEDNESDAY</t>
+  </si>
+  <si>
+    <t>Beef Vindaloo</t>
+  </si>
+  <si>
+    <t>Garlic Fish</t>
+  </si>
+  <si>
+    <t>Paneer Butter Masala</t>
+  </si>
+  <si>
+    <t>THURSDAY</t>
+  </si>
+  <si>
+    <t>Veg Pulao</t>
+  </si>
+  <si>
+    <t>Chicken Kolhapuri</t>
+  </si>
+  <si>
+    <t>Aalo Gobi Capsicum</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -969,13 +880,6 @@
       <color theme="1"/>
       <name val="Helvetica"/>
       <family val="18"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -998,15 +902,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9076,992 +8977,1528 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C92B042-D4FF-2640-8B1F-B7EB4E9D16D9}">
-  <dimension ref="A1:D189"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60493718-0AF5-4082-ABAF-9F31032F6672}">
+  <dimension ref="A1:D134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="A2" t="s">
         <v>210</v>
       </c>
-      <c r="D2">
-        <v>2</v>
+      <c r="B2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C3" s="2" t="s">
-        <v>7</v>
+      <c r="A3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
+      <c r="A4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>210</v>
+      </c>
+      <c r="B8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>210</v>
+      </c>
+      <c r="B11" t="s">
+        <v>220</v>
+      </c>
+      <c r="C11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>210</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B16" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="2" t="s">
+      <c r="C16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>210</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" t="s">
+        <v>211</v>
+      </c>
+      <c r="C18" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>210</v>
+      </c>
+      <c r="B19" t="s">
+        <v>228</v>
+      </c>
+      <c r="C19" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>210</v>
+      </c>
+      <c r="B20" t="s">
+        <v>228</v>
+      </c>
+      <c r="C20" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B21" t="s">
+        <v>211</v>
+      </c>
+      <c r="C21" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C9" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C10" s="2" t="s">
+      <c r="D21" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C11" s="2" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>231</v>
+      </c>
+      <c r="B22" t="s">
+        <v>211</v>
+      </c>
+      <c r="C22" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>231</v>
+      </c>
+      <c r="B23" t="s">
+        <v>215</v>
+      </c>
+      <c r="C23" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>231</v>
+      </c>
+      <c r="B24" t="s">
+        <v>215</v>
+      </c>
+      <c r="C24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>231</v>
+      </c>
+      <c r="B25" t="s">
+        <v>215</v>
+      </c>
+      <c r="C25" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>231</v>
+      </c>
+      <c r="B26" t="s">
+        <v>215</v>
+      </c>
+      <c r="C26" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>231</v>
+      </c>
+      <c r="B27" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>231</v>
+      </c>
+      <c r="B28" t="s">
+        <v>215</v>
+      </c>
+      <c r="C28" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>231</v>
+      </c>
+      <c r="B29" t="s">
+        <v>215</v>
+      </c>
+      <c r="C29" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>231</v>
+      </c>
+      <c r="B30" t="s">
+        <v>220</v>
+      </c>
+      <c r="C30" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>231</v>
+      </c>
+      <c r="B31" t="s">
+        <v>220</v>
+      </c>
+      <c r="C31" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>231</v>
+      </c>
+      <c r="B32" t="s">
+        <v>223</v>
+      </c>
+      <c r="C32" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>231</v>
+      </c>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>231</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>231</v>
+      </c>
+      <c r="B35" t="s">
+        <v>211</v>
+      </c>
+      <c r="C35" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>231</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>231</v>
+      </c>
+      <c r="B37" t="s">
+        <v>211</v>
+      </c>
+      <c r="C37" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>231</v>
+      </c>
+      <c r="B38" t="s">
+        <v>228</v>
+      </c>
+      <c r="C38" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>231</v>
+      </c>
+      <c r="B39" t="s">
+        <v>228</v>
+      </c>
+      <c r="C39" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>243</v>
+      </c>
+      <c r="B40" t="s">
+        <v>211</v>
+      </c>
+      <c r="C40" t="s">
+        <v>212</v>
+      </c>
+      <c r="D40" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>243</v>
+      </c>
+      <c r="B41" t="s">
+        <v>211</v>
+      </c>
+      <c r="C41" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>243</v>
+      </c>
+      <c r="B42" t="s">
+        <v>215</v>
+      </c>
+      <c r="C42" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>243</v>
+      </c>
+      <c r="B43" t="s">
+        <v>215</v>
+      </c>
+      <c r="C43" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>243</v>
+      </c>
+      <c r="B44" t="s">
+        <v>215</v>
+      </c>
+      <c r="C44" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>243</v>
+      </c>
+      <c r="B45" t="s">
+        <v>215</v>
+      </c>
+      <c r="C45" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>243</v>
+      </c>
+      <c r="B46" t="s">
+        <v>215</v>
+      </c>
+      <c r="C46" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>243</v>
+      </c>
+      <c r="B47" t="s">
+        <v>215</v>
+      </c>
+      <c r="C47" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>243</v>
+      </c>
+      <c r="B48" t="s">
+        <v>220</v>
+      </c>
+      <c r="C48" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>243</v>
+      </c>
+      <c r="B49" t="s">
+        <v>220</v>
+      </c>
+      <c r="C49" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>243</v>
+      </c>
+      <c r="B50" t="s">
+        <v>220</v>
+      </c>
+      <c r="C50" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>243</v>
+      </c>
+      <c r="B51" t="s">
+        <v>223</v>
+      </c>
+      <c r="C51" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>243</v>
+      </c>
+      <c r="B52" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>243</v>
+      </c>
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>243</v>
+      </c>
+      <c r="B54" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>243</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>243</v>
+      </c>
+      <c r="B56" t="s">
+        <v>211</v>
+      </c>
+      <c r="C56" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>243</v>
+      </c>
+      <c r="B57" t="s">
+        <v>228</v>
+      </c>
+      <c r="C57" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>243</v>
+      </c>
+      <c r="B58" t="s">
+        <v>228</v>
+      </c>
+      <c r="C58" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>248</v>
+      </c>
+      <c r="B59" t="s">
+        <v>211</v>
+      </c>
+      <c r="C59" t="s">
+        <v>212</v>
+      </c>
+      <c r="D59" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>248</v>
+      </c>
+      <c r="B60" t="s">
+        <v>211</v>
+      </c>
+      <c r="C60" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>248</v>
+      </c>
+      <c r="B61" t="s">
+        <v>215</v>
+      </c>
+      <c r="C61" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>248</v>
+      </c>
+      <c r="B62" t="s">
+        <v>215</v>
+      </c>
+      <c r="C62" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>248</v>
+      </c>
+      <c r="B63" t="s">
+        <v>215</v>
+      </c>
+      <c r="C63" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>248</v>
+      </c>
+      <c r="B64" t="s">
+        <v>215</v>
+      </c>
+      <c r="C64" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>248</v>
+      </c>
+      <c r="B65" t="s">
+        <v>215</v>
+      </c>
+      <c r="C65" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>248</v>
+      </c>
+      <c r="B66" t="s">
+        <v>215</v>
+      </c>
+      <c r="C66" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>248</v>
+      </c>
+      <c r="B67" t="s">
+        <v>220</v>
+      </c>
+      <c r="C67" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>248</v>
+      </c>
+      <c r="B68" t="s">
+        <v>220</v>
+      </c>
+      <c r="C68" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>248</v>
+      </c>
+      <c r="B69" t="s">
+        <v>223</v>
+      </c>
+      <c r="C69" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>248</v>
+      </c>
+      <c r="B70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>248</v>
+      </c>
+      <c r="B71" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>248</v>
+      </c>
+      <c r="B72" t="s">
+        <v>211</v>
+      </c>
+      <c r="C72" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>248</v>
+      </c>
+      <c r="B73" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>248</v>
+      </c>
+      <c r="B74" t="s">
+        <v>211</v>
+      </c>
+      <c r="C74" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>248</v>
+      </c>
+      <c r="B75" t="s">
+        <v>228</v>
+      </c>
+      <c r="C75" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>248</v>
+      </c>
+      <c r="B76" t="s">
+        <v>228</v>
+      </c>
+      <c r="C76" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>254</v>
+      </c>
+      <c r="B77" t="s">
+        <v>211</v>
+      </c>
+      <c r="C77" t="s">
+        <v>212</v>
+      </c>
+      <c r="D77" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>254</v>
+      </c>
+      <c r="B78" t="s">
+        <v>211</v>
+      </c>
+      <c r="C78" t="s">
+        <v>255</v>
+      </c>
+      <c r="D78" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>254</v>
+      </c>
+      <c r="B79" t="s">
+        <v>215</v>
+      </c>
+      <c r="C79" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>254</v>
+      </c>
+      <c r="B80" t="s">
+        <v>215</v>
+      </c>
+      <c r="C80" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>254</v>
+      </c>
+      <c r="B81" t="s">
+        <v>215</v>
+      </c>
+      <c r="C81" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>254</v>
+      </c>
+      <c r="B82" t="s">
+        <v>215</v>
+      </c>
+      <c r="C82" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>254</v>
+      </c>
+      <c r="B83" t="s">
+        <v>215</v>
+      </c>
+      <c r="C83" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>254</v>
+      </c>
+      <c r="B84" t="s">
+        <v>215</v>
+      </c>
+      <c r="C84" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>254</v>
+      </c>
+      <c r="B85" t="s">
+        <v>215</v>
+      </c>
+      <c r="C85" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>254</v>
+      </c>
+      <c r="B86" t="s">
+        <v>220</v>
+      </c>
+      <c r="C86" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>254</v>
+      </c>
+      <c r="B87" t="s">
+        <v>220</v>
+      </c>
+      <c r="C87" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>254</v>
+      </c>
+      <c r="B88" t="s">
+        <v>223</v>
+      </c>
+      <c r="C88" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>254</v>
+      </c>
+      <c r="B89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>254</v>
+      </c>
+      <c r="B90" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>254</v>
+      </c>
+      <c r="B91" t="s">
+        <v>211</v>
+      </c>
+      <c r="C91" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>254</v>
+      </c>
+      <c r="B92" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>254</v>
+      </c>
+      <c r="B93" t="s">
+        <v>211</v>
+      </c>
+      <c r="C93" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>254</v>
+      </c>
+      <c r="B94" t="s">
+        <v>228</v>
+      </c>
+      <c r="C94" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>254</v>
+      </c>
+      <c r="B95" t="s">
+        <v>228</v>
+      </c>
+      <c r="C95" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>263</v>
+      </c>
+      <c r="B96" t="s">
+        <v>211</v>
+      </c>
+      <c r="C96" t="s">
+        <v>212</v>
+      </c>
+      <c r="D96" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>263</v>
+      </c>
+      <c r="B97" t="s">
+        <v>211</v>
+      </c>
+      <c r="C97" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="2" t="s">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>263</v>
+      </c>
+      <c r="B98" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="2" t="s">
+      <c r="C98" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>263</v>
+      </c>
+      <c r="B99" t="s">
+        <v>215</v>
+      </c>
+      <c r="C99" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>263</v>
+      </c>
+      <c r="B100" t="s">
+        <v>215</v>
+      </c>
+      <c r="C100" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>263</v>
+      </c>
+      <c r="B101" t="s">
+        <v>215</v>
+      </c>
+      <c r="C101" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>263</v>
+      </c>
+      <c r="B102" t="s">
+        <v>215</v>
+      </c>
+      <c r="C102" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>263</v>
+      </c>
+      <c r="B103" t="s">
+        <v>215</v>
+      </c>
+      <c r="C103" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>263</v>
+      </c>
+      <c r="B104" t="s">
+        <v>215</v>
+      </c>
+      <c r="C104" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>263</v>
+      </c>
+      <c r="B105" t="s">
+        <v>220</v>
+      </c>
+      <c r="C105" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>263</v>
+      </c>
+      <c r="B106" t="s">
+        <v>220</v>
+      </c>
+      <c r="C106" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>263</v>
+      </c>
+      <c r="B107" t="s">
+        <v>223</v>
+      </c>
+      <c r="C107" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>263</v>
+      </c>
+      <c r="B108" t="s">
+        <v>8</v>
+      </c>
+      <c r="C108" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>263</v>
+      </c>
+      <c r="B109" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>263</v>
+      </c>
+      <c r="B110" t="s">
+        <v>211</v>
+      </c>
+      <c r="C110" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>263</v>
+      </c>
+      <c r="B111" t="s">
+        <v>8</v>
+      </c>
+      <c r="C111" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>263</v>
+      </c>
+      <c r="B112" t="s">
+        <v>211</v>
+      </c>
+      <c r="C112" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>263</v>
+      </c>
+      <c r="B113" t="s">
+        <v>228</v>
+      </c>
+      <c r="C113" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>263</v>
+      </c>
+      <c r="B114" t="s">
+        <v>228</v>
+      </c>
+      <c r="C114" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>267</v>
+      </c>
+      <c r="B115" t="s">
+        <v>211</v>
+      </c>
+      <c r="C115" t="s">
+        <v>212</v>
+      </c>
+      <c r="D115" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>267</v>
+      </c>
+      <c r="B116" t="s">
+        <v>211</v>
+      </c>
+      <c r="C116" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>267</v>
+      </c>
+      <c r="B117" t="s">
+        <v>215</v>
+      </c>
+      <c r="C117" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>267</v>
+      </c>
+      <c r="B118" t="s">
+        <v>215</v>
+      </c>
+      <c r="C118" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>267</v>
+      </c>
+      <c r="B119" t="s">
+        <v>215</v>
+      </c>
+      <c r="C119" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="2" t="s">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>267</v>
+      </c>
+      <c r="B120" t="s">
+        <v>215</v>
+      </c>
+      <c r="C120" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>267</v>
+      </c>
+      <c r="B121" t="s">
+        <v>215</v>
+      </c>
+      <c r="C121" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>267</v>
+      </c>
+      <c r="B122" t="s">
+        <v>215</v>
+      </c>
+      <c r="C122" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>267</v>
+      </c>
+      <c r="B123" t="s">
+        <v>215</v>
+      </c>
+      <c r="C123" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>267</v>
+      </c>
+      <c r="B124" t="s">
+        <v>215</v>
+      </c>
+      <c r="C124" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C17" s="2" t="s">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>267</v>
+      </c>
+      <c r="B125" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C18" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C19" s="2" t="s">
+      <c r="C125" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C20" s="2" t="s">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>267</v>
+      </c>
+      <c r="B126" t="s">
+        <v>220</v>
+      </c>
+      <c r="C126" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C21" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C22" s="2" t="s">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>267</v>
+      </c>
+      <c r="B127" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C23" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C24" s="2" t="s">
+      <c r="C127" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>267</v>
+      </c>
+      <c r="B128" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C26" s="2" t="s">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>267</v>
+      </c>
+      <c r="B129" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>267</v>
+      </c>
+      <c r="B130" t="s">
+        <v>211</v>
+      </c>
+      <c r="C130" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>267</v>
+      </c>
+      <c r="B131" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C28" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C29" s="2" t="s">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>267</v>
+      </c>
+      <c r="B132" t="s">
+        <v>211</v>
+      </c>
+      <c r="C132" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C30" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C31" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C32" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C33" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C34" s="2" t="s">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>267</v>
+      </c>
+      <c r="B133" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C35" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C36" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C37" s="2" t="s">
+      <c r="C133" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>267</v>
+      </c>
+      <c r="B134" t="s">
+        <v>228</v>
+      </c>
+      <c r="C134" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C38" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C39" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C40" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C41" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C42" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C43" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C44" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C45" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C46" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C47" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C48" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C49" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C50" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C52" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C53" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="C54" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C55" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C56" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C57" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C58" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C59" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C60" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C61" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C62" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C63" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C64" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C65" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C66" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C67" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C68" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C69" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C70" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C71" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C72" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C73" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C74" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C75" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C76" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C77" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C78" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C80" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C81" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C82" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C83" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C84" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C85" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C86" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C87" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C88" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C89" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C90" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C91" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C92" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C93" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C94" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C95" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C96" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C97" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C98" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C99" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C100" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C101" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C102" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C103" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C104" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C105" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C106" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C108" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C109" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C110" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C111" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C112" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C113" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C114" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C115" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C116" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C117" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C118" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C119" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C120" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C121" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C122" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C123" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C124" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C125" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="126" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C126" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C127" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C128" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C129" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C130" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C131" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C132" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C133" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C134" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C136" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C137" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C138" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C139" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C140" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C141" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C142" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C143" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C144" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C145" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C146" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C147" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C148" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C149" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C150" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="151" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C151" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="152" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C152" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="153" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C153" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="154" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C154" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="155" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C155" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="156" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C156" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="157" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C157" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C158" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C159" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C160" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C161" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C162" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C164" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C165" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C166" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C167" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C168" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C169" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C170" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C171" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C172" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C173" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C174" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C175" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C176" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="177" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C177" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="178" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C178" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="179" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C179" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="180" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C180" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="181" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C181" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="182" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C182" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="183" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C183" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="184" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C184" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="185" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C185" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="186" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C186" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="187" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C187" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="188" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C188" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="189" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C189" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91C3AD69-3D4C-4C60-8E1B-122A3BE35217}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
